--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K22" headerRowCount="1">
-  <autoFilter ref="A1:K22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K17" headerRowCount="1">
+  <autoFilter ref="A1:K17"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -149,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K26" headerRowCount="1">
-  <autoFilter ref="A1:K26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K31" headerRowCount="1">
+  <autoFilter ref="A1:K31"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -457,16 +457,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -572,12 +572,12 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>North America's leading conference focused on Industrial AI, SCADA technology, and digital transformation for manufacturing and utilities professionals. Features 60+ speakers, 3 tech tracks (AI Manufacturing, Industrial AI 101 for SMEs, SCADA Technology &amp; AI Utilities), 8+ networking events, and 1x1 meetings between buyers and solution providers. Registration rates: Super Early Bird $595 (ended April 24), Early Bird $795 (ended June 26), Regular Rate $995 (ends August 17).</t>
+          <t>North America's #1 Conference in Industrial AI, bringing together manufacturing, SCADA, IT/OT, cybersecurity, and automation professionals for 3 days of cutting-edge content, 60+ speakers, and 8+ networking events. Features three tech tracks: AI Manufacturing, Industrial AI 101 for SMEs, and SCADA Technology &amp; AI Utilities.</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>In-person educational AI conference in Atlanta with strong focus on Industrial AI and manufacturing, though the tiered paid registration structure and vendor-focused networking suggest some commercial emphasis.</t>
+          <t>In-person conference in Atlanta with strong AI/automation focus, 3 days, 60+ speakers, and multiple specialized tracks makes it an excellent fit, though the lack of information about cost and whether it's primarily a sales pitch prevents a perfect 5.</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear AI/ML content (machine learning applications), but lacks Georgia-focus or Georgia institution affiliation, and appears to be a paid training course rather than an educational discussion.</t>
+          <t>Virtual-only event with clear AI/ML content (machine learning, Python) but no indication of Georgia focus or Georgia institution hosting, and the course structure suggests paid training rather than educational discussion.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear AI/ML content (generative AI, prompt engineering, automation) but no indication of Georgia focus or Georgia institution hosting, and appears to be a paid training course rather than an educational discussion.</t>
+          <t>Virtual-only event with clear AI/ML content (generative AI, prompt engineering, automation) but no indication of Georgia focus or Georgia institution hosting, appearing to be a general paid training course rather than an educational discussion.</t>
         </is>
       </c>
     </row>
@@ -742,18 +742,18 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>In-person event at Georgia Tech with clear AI/ML content (generative AI, prompt engineering, practical applications), though the course nature and paid training format prevent a perfect score.</t>
+          <t>In-person event at Georgia Tech with clear AI/ML focus covering generative AI fundamentals and practical applications, though it appears to be a paid training course with some commercial aspects.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Pla...</t>
+          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>August 5, 2026</t>
+          <t>August 18, 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -775,11 +775,7 @@
           <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>11:00 AM - 1:30 PM EDT</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
@@ -788,19 +784,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>An event focused on manufacturing technology challenges and practical solutions for today's plant, hosted by the Georgia Manufacturing Alliance.</t>
+          <t>An AI conference where GMA participates as a special exhibitor and moderator, running from August 18 to August 20, 2026.</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>Virtual event hosted by Georgia institution (Georgia Manufacturing Alliance) is a positive factor, but the complete absence of any mention of AI, machine learning, or automation in the description triggers the automatic 1 rule, resulting in a score of 2 due to Georgia hosting alone.</t>
+          <t>The event clearly involves AI and is multi-day, but the missing location details prevent confirmation of Georgia focus, and the vague description about GMA's role raises uncertainty about whether this is educational or sales-focused.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
+          <t>Welcome to the ATL AI Community! Networking &amp; Ecosystem Spotlight presented by TAG Data Science &amp; AI Society</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -813,7 +809,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>August 18 - August 20, 2026</t>
+          <t>July 1, 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -823,10 +819,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
@@ -835,23 +835,23 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>An AI conference where the Georgia Manufacturing Alliance participates as a special exhibitor and moderator.</t>
+          <t>Join technology leaders, founders, practitioners, researchers, investors, students, and community builders for an evening focused on connection, visibility, and conversation around the future of AI in Atlanta.</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>In-person AI conference with Georgia Manufacturing Alliance participation suggests Georgia focus, but incomplete details (missing location, times, and signup link) prevent higher confidence that the event is actually held in Georgia.</t>
+          <t>In-person Georgia AI networking event hosted by TAG (a Georgia institution) with clear AI focus and community-building emphasis, but confidence is medium due to missing venue details and no description of specific educational content.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Welcome to the ATL AI Community! Networking &amp; Ecosystem Spotlight presented by TAG Data Science &amp; AI Society</t>
+          <t>The TAG Fintech Innovation Challenge: Where Are They Now? presented by TAG Fintech Society</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>July 1, 2026</t>
+          <t>July 28, 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -886,19 +886,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>Join technology leaders, founders, practitioners, researchers, investors, students, and community builders for an evening focused on connection, visibility, and conversation around the future of AI in Atlanta.</t>
+          <t>A captivating panel discussion where three fintech founders share experiences growing their companies from the ground up.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>In-person Georgia event (Atlanta) hosted by TAG, a Georgia institution, with clear AI focus and educational/networking value, but confidence is medium due to missing location details and no signup link provided.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like TAG hosting and in-person format.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Rural AI Workforce Forum 2026</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>July 7, 2026</t>
+          <t>August 6-7, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>4:00 PM - 1:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -937,19 +937,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>This 30-minute session is led by Lili Orozco from Member Services. This session will focus on TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
+          <t>Preparing rural communities for an AI-driven future.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event hosted by Georgia institution (TAG) with no mention of AI/ML/automation content, making it ineligible for higher scores despite the Georgia-focused organizer.</t>
+          <t>Event mentions AI and is in-person, but critical details are missing (no location specified, making it impossible to determine if it's in Georgia), and the vague description provides insufficient information to assess whether it's educational content or a sales pitch.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Israeli Cybersecurity Summit</t>
+          <t>Fintech South 2026</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -957,12 +957,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>July 29, 2026</t>
+          <t>August 18, 2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5:00 PM - 8:00 PM</t>
+          <t>8:00 AM - 7:00 PM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -989,14 +989,14 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 score, and the location is unspecified so Georgia presence cannot be confirmed.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rural AI Workforce Forum 2026</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>August 6-7, 2026</t>
+          <t>September 1, 2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4:00 PM - 1:00 PM</t>
+          <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1035,23 +1035,23 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>Preparing rural communities for an AI-driven future.</t>
+          <t>Monthly introduction session to TAG membership.</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Event clearly mentions AI and is in-person, but critical details are missing (no location specified, cannot confirm Georgia connection, unclear if educational or sales-focused), preventing a higher score despite the multi-day format.</t>
+          <t>Virtual-only membership orientation hosted by Georgia institution (TAG) but lacks any mention of AI/machine learning content, making it primarily an administrative event rather than educational AI content.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fintech South 2026</t>
+          <t>TAG-Ed 2026 Pathways to Leadership Summit &amp; Graduation</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>August 18, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8:00 AM - 7:00 PM</t>
+          <t>10:00 AM - 3:00 PM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1087,14 +1087,14 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Event details lack any mention of AI, machine learning, or automation, and insufficient information is provided to assess other criteria.</t>
+          <t>Event is hosted by TAG (a Georgia institution) and in-person, which are positive factors, but the complete absence of any mention of AI, machine learning, or automation in the provided details triggers the automatic 1 rating, though being Georgia-based prevents a lower score.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>//Shift AI 2026</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>September 1, 2026</t>
+          <t>September 18, 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>8:00 AM - 3:00 PM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1133,19 +1133,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>Monthly introduction session to TAG membership.</t>
+          <t>Join us for our kickoff AI Summit Event!</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event hosted by TAG (Georgia institution) scores higher than generic virtual events, but lacks any mention of AI/ML content and appears to be a membership orientation rather than educational programming.</t>
+          <t>While the event clearly mentions AI and appears to be in-person, the lack of location information (critical for determining if it's in Georgia), missing signup details, and vague description prevent a higher rating.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TAG-Ed 2026 Pathways to Leadership Summit &amp; Graduation</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>October 6, 2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10:00 AM - 3:00 PM</t>
+          <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1182,21 +1182,25 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>Monthly introduction session to TAG membership.</t>
+        </is>
+      </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Event is hosted by TAG (a Georgia institution) and appears to be in-person, which would normally score higher, but the complete absence of any mention of AI, machine learning, or automation in the description triggers the automatic 1 rule, though the Georgia-hosted status prevents it from being a pure 1.</t>
+          <t>Virtual-only event hosted by Georgia institution (TAG) but lacks any mention of AI/ML/automation content, making it an introductory membership session rather than an educational AI event.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>//Shift AI 2026</t>
+          <t>Annual DataPalooza presented by TAG Data Governance Society</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1205,7 +1209,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>September 18, 2026</t>
+          <t>October 8, 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1220,7 +1224,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8:00 AM - 3:00 PM</t>
+          <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1229,34 +1233,30 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>Kickoff AI Summit Event.</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Event clearly mentions AI and is in-person, but lacks critical details including location (cannot confirm if in Georgia), signup link, and substantive description to assess whether it's educational or a sales pitch.</t>
+          <t>TAG is a Georgia institution and DataPalooza suggests an educational data/AI event, but the missing location details, event description, and no explicit mention of AI content prevent a higher score.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>TAG Chairs' Gala 2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>October 6, 2026</t>
+          <t>November 19, 2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>6:00 PM - 11:00 PM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1280,36 +1280,28 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>Monthly introduction session to TAG membership.</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event hosted by Georgia institution (TAG) but lacks any mention of AI, machine learning, or automation content, making it an automatic 1 that is only elevated to 2 due to TAG's Georgia focus.</t>
+          <t>Event details lack any mention of AI, machine learning, or automation, and the description is too vague to assess whether it focuses on these topics.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Annual DataPalooza presented by TAG Data Governance Society</t>
+          <t>Leading Through the AI Shift: Strategy, Risk &amp; IP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>October 8, 2026</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>June 30, 2026</t>
@@ -1320,260 +1312,21 @@
           <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>5:30 PM - 7:30 PM</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>An insightful one-hour program hosted by Taft on navigating the legal and strategic challenges of artificial intelligence in today's business environment.</t>
+        </is>
+      </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Event is in-person and hosted by TAG (Georgia-based organization) which suggests good fit, but lack of location confirmation, missing description, and no explicit mention of AI/ML content creates significant uncertainty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>November 3, 2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>June 30, 2026</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>12:30 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>Monthly introduction session to TAG membership.</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>Virtual-only event hosted by Georgia institution (TAG) but lacks any mention of AI/ML content, appearing to be a general membership orientation rather than an educational AI event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>[Pending] Veterans Day presented by TAG Infrastructure Society</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>November 5, 2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>June 30, 2026</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>11:30 AM - 2:00 PM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>Event details are insufficient to assess (no description provided, unclear if AI/ML/automation-related, and '[Pending]' status suggests incomplete information), but the title suggests a Veterans Day event with no apparent connection to AI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TAG Chairs' Gala 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>November 19, 2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>June 30, 2026</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6:00 PM - 11:00 PM</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other factors like the Georgia-based TAG organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>December 1, 2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>June 30, 2026</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>12:30 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>Monthly introduction session to TAG membership.</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>Virtual-only event hosted by Georgia institution (TAG) but lacks any mention of AI, machine learning, or automation content, making it primarily a membership orientation rather than an educational AI event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Leading Through the AI Shift: Strategy, Risk &amp; IP</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>June 30, 2026</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>An insightful one-hour program hosted by Taft on navigating the legal and strategic challenges of artificial intelligence in today's business environment.</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>Virtual-only event with AI content (legal/strategy focus) but hosted by Taft (a law firm, not a Georgia institution) with insufficient detail about Georgia relevance or educational depth.</t>
+          <t>Virtual-only event with AI content but hosted by Taft (a law firm, not a Georgia institution) with no Georgia focus indicated, making it a generic corporate webinar despite relevant AI topic.</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1765,12 +1518,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>A morning networking coffee and connections event hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
+          <t>A morning networking coffee and connections event in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1573,7 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>A networking luncheon hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
+          <t>A networking luncheon in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
@@ -1880,7 +1633,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1688,7 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of location or other factors.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 according to the criteria.</t>
         </is>
       </c>
     </row>
@@ -1985,19 +1738,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>An afternoon session of the Murray Plastics factory tour in Gainesville, held as a joint event with SMTA.</t>
+          <t>An afternoon session of the factory tour at Murray Plastics in Gainesville, held as a joint event with SMTA.</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor regardless of location or format.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the first criterion.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Women of GMA Virtual Networking Event 8/11/26</t>
+          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Plants</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2010,7 +1763,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>August 11, 2026</t>
+          <t>August 5, 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2025,14 +1778,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3:30 PM - 4:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>11:00 AM - 1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2040,19 +1789,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>A virtual networking event hosted by Women of GMA (WGMA).</t>
+          <t>An event focused on manufacturing technology challenges and practical solutions for today's plants, hosted by the Georgia Manufacturing Alliance.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other factors.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coffee and Connections - Atlanta 8-20-2026</t>
+          <t>Women of GMA Virtual Networking Event 8/11/26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2065,7 +1814,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>August 20, 2026</t>
+          <t>August 11, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2080,12 +1829,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8:30 AM - 10:00 AM EDT</t>
+          <t>3:30 PM - 4:30 PM EDT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2095,19 +1844,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>A morning networking coffee and connections event hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
+          <t>A virtual networking event for Women of GMA members.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Networking Luncheon - Atlanta 8-20-2026</t>
+          <t>Coffee and Connections - Atlanta 8-20-2026</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2135,7 +1884,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11:30 AM - 1:00 PM EDT</t>
+          <t>8:30 AM - 10:00 AM EDT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2150,19 +1899,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>A networking luncheon hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
+          <t>A morning networking coffee and connections event in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026 Georgia Manufacturing Summit</t>
+          <t>Networking Luncheon - Atlanta 8-20-2026</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2175,7 +1924,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>August 20, 2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2190,12 +1939,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7:00 AM - 4:00 PM EDT</t>
+          <t>11:30 AM - 1:00 PM EDT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2205,19 +1954,19 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>The annual Georgia Manufacturing Summit, a signature event hosted by the Georgia Manufacturing Alliance bringing together manufacturing professionals across the state.</t>
+          <t>A networking luncheon in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>2026 Georgia Manufacturing Summit</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2230,7 +1979,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>July 6, 2026</t>
+          <t>September 15, 2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2240,15 +1989,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>7:00 AM - 4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2256,19 +2009,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>The annual Georgia Manufacturing Summit, a signature event hosted by the Georgia Manufacturing Alliance bringing together manufacturing professionals across the state.</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the first criterion.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Superfans and Customer Loyalty: Strategies That Convert Customer Acquisition into Long-Term Advocacy presented by TAG CX Society</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2281,7 +2034,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 6, 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2296,7 +2049,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3:00 PM - 6:30 PM</t>
+          <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2307,19 +2060,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>This event explores how brands can turn event-driven customer acquisition into long-term loyalty, owned relationships, and measurable customer value.</t>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IBM SkillsBuild Orientation</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2332,7 +2085,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 7, 2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2347,7 +2100,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6:00 PM - 7:00 PM</t>
+          <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2358,19 +2111,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>A mandatory virtual orientation to kick off the upcoming cohort. Participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
+          <t>This 30-minute session is led by Lili Orozco from Member Services, focusing on TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic 1 rating regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Building Impact Together: A Tech Collaboration &amp; Volunteer Event</t>
+          <t>Superfans and Customer Loyalty: Strategies That Convert Customer Acquisition into Long-Term Advocacy presented by TAG CX Society</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2383,7 +2136,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>July 17, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2398,7 +2151,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10:00 AM - 3:00 PM</t>
+          <t>3:00 PM - 6:30 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2407,17 +2160,21 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>This event explores how brands can turn event-driven customer acquisition into long-term loyalty, owned relationships, and measurable customer value.</t>
+        </is>
+      </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like TAG hosting and in-person format.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Summer 2026 Social presented by TAG Digital Health Society</t>
+          <t>IBM SkillsBuild Orientation</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2430,7 +2187,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>July 21, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2445,7 +2202,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5:30 PM - 7:30 PM</t>
+          <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2456,19 +2213,19 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>Join TAG's Digital Health Society for an evening of connection and collaboration at the 2026 Summer Social!</t>
+          <t>A mandatory virtual orientation to kick off the upcoming cohort. Participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The TAG Fintech Innovation Challenge: Where Are They Now? presented by TAG Fintech Society</t>
+          <t>Building Impact Together: A Tech Collaboration &amp; Volunteer Event</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2481,7 +2238,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>July 28, 2026</t>
+          <t>July 17, 2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2496,7 +2253,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5:30 PM - 7:30 PM</t>
+          <t>10:00 AM - 3:00 PM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2505,21 +2262,17 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>A captivating panel discussion where three fintech founders share experiences growing their companies from the ground up.</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like TAG hosting and in-person format.</t>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>Summer 2026 Social presented by TAG Digital Health Society</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2532,7 +2285,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>August 3, 2026</t>
+          <t>July 21, 2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2547,7 +2300,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2558,19 +2311,19 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>Join TAG's Digital Health Society for an evening of connection and collaboration at their 2026 Summer Social.</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Israeli Cybersecurity Summit</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2583,7 +2336,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>August 4, 2026</t>
+          <t>July 29, 2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2598,7 +2351,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>5:00 PM - 8:00 PM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2607,14 +2360,10 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>This 30-minute session focuses on TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>The event contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2383,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>September 14, 2026</t>
+          <t>August 3, 2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2665,14 +2414,14 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>The event description makes zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other factors.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2685,7 +2434,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>October 5, 2026</t>
+          <t>August 4, 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2700,7 +2449,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2711,19 +2460,19 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>This 30-minute session is led by Lili Orozco from Member Services, focusing on TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like TAG hosting and in-person format.</t>
+          <t>The event contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other factors.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026 TAG Invest Connect: Meet, Pitch, &amp; Partner</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2736,7 +2485,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>October 22, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2751,7 +2500,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1:00 PM - 5:00 PM</t>
+          <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2762,12 +2511,12 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>TAG Invest Connect is an annual event that connects Black tech entrepreneurs with the opportunity to pitch to investors looking for innovative companies.</t>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like being a TAG-hosted in-person event in Georgia.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2536,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>November 2, 2026</t>
+          <t>October 5, 2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2818,14 +2567,14 @@
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like being hosted by TAG in Georgia.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026 Georgia Day of Code</t>
+          <t>2026 TAG Invest Connect: Meet, Pitch, &amp; Partner</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2838,7 +2587,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>December 4, 2026</t>
+          <t>October 22, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2853,7 +2602,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9:00 AM - 3:00 PM</t>
+          <t>1:00 PM - 5:00 PM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2864,12 +2613,12 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>A free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
+          <t>TAG Invest Connect is an annual event that connects Black tech entrepreneurs with the opportunity to pitch to investors looking for innovative companies.</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>The event description makes zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other positive factors like TAG hosting and in-person format.</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2638,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>December 7, 2026</t>
+          <t>November 2, 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2920,14 +2669,14 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like being hosted by TAG (a Georgia AI organization) and being in-person.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like being in-person and hosted by TAG.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mastercard Small Business Summit</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2938,7 +2687,11 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>November 3, 2026</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>June 30, 2026</t>
@@ -2949,7 +2702,11 @@
           <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -2958,12 +2715,255 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>Mastercard's third annual Small Business Summit series convening entrepreneurs, financial institutions, local leaders, and industry experts during National Small Business Month. One-day events delivering hands-on education, mentorship, and practical resources for small businesses.</t>
+          <t>Monthly introduction session to TAG membership.</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>[Pending] Veterans Day presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>November 5, 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>11:30 AM - 2:00 PM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>Event details contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>December 1, 2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>Monthly introduction session to TAG membership.</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026 Georgia Day of Code</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>December 4, 2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>9:00 AM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>A free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>December 7, 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like it being hosted by TAG (a Georgia institution) and in-person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mastercard Small Business Summit</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>Mastercard's third annual Small Business Summit series convening entrepreneurs, financial institutions, local leaders, and industry experts during National Small Business Month with hands-on education, mentorship, and practical resources.</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying criterion.</t>
         </is>
       </c>
     </row>

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K17" headerRowCount="1">
-  <autoFilter ref="A1:K17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K45" headerRowCount="1">
+  <autoFilter ref="A1:K45"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -149,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K31" headerRowCount="1">
-  <autoFilter ref="A1:K31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K64" headerRowCount="1">
+  <autoFilter ref="A1:K64"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -457,16 +457,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -572,12 +572,12 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>North America's #1 Conference in Industrial AI, bringing together manufacturing, SCADA, IT/OT, cybersecurity, and automation professionals for 3 days of cutting-edge content, 60+ speakers, and 8+ networking events. Features three tech tracks: AI Manufacturing, Industrial AI 101 for SMEs, and SCADA Technology &amp; AI Utilities.</t>
+          <t>North America's #1 Conference in Industrial AI, bringing together manufacturing, SCADA, IT/OT, and cybersecurity professionals to accelerate digital transformation and industrial automation. Features 60+ speakers, 350+ attendees, three tech tracks (AI Manufacturing, Industrial AI 101 for SMEs, SCADA Technology &amp; AI Utilities), and 8+ networking events over three days.</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>In-person conference in Atlanta with strong AI/automation focus, 3 days, 60+ speakers, and multiple specialized tracks makes it an excellent fit, though the lack of information about cost and whether it's primarily a sales pitch prevents a perfect 5.</t>
+          <t>Excellent fit: in-person event in Atlanta, Georgia; substantial multi-day conference with 60+ speakers and 350+ attendees; strong focus on AI and industrial automation across three technical tracks; educational content for both advanced practitioners and SMEs; prominent networking component.</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear AI/ML content (machine learning, Python) but no indication of Georgia focus or Georgia institution hosting, and the course structure suggests paid training rather than educational discussion.</t>
+          <t>Virtual-only event with clear AI/ML content but no indication of Georgia focus or hosting by Georgia institution, making it ineligible for higher scoring despite educational value.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear AI/ML content (generative AI, prompt engineering, automation) but no indication of Georgia focus or Georgia institution hosting, appearing to be a general paid training course rather than an educational discussion.</t>
+          <t>Virtual-only event with clear AI/ML content (generative AI, prompt engineering, automation) but no indication of Georgia focus or Georgia institution hosting, making it a national corporate-style course that scores at the low end for virtual events.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>In-person event at Georgia Tech with clear AI/ML focus covering generative AI fundamentals and practical applications, though it appears to be a paid training course with some commercial aspects.</t>
+          <t>In-person Georgia Tech event with clear AI/ML focus (generative AI, prompt engineering, practical applications) that appears educational rather than sales-driven, though the late 8 PM start time is slightly unusual.</t>
         </is>
       </c>
     </row>
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>August 18, 2026</t>
+          <t>August 18 - August 20, 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,32 +784,32 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>An AI conference where GMA participates as a special exhibitor and moderator, running from August 18 to August 20, 2026.</t>
+          <t>An AI conference where the Georgia Manufacturing Alliance participates as a special exhibitor and moderator.</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>The event clearly involves AI and is multi-day, but the missing location details prevent confirmation of Georgia focus, and the vague description about GMA's role raises uncertainty about whether this is educational or sales-focused.</t>
+          <t>In-person AI conference with Georgia Manufacturing Alliance involvement suggests strong Georgia relevance, but incomplete details (missing location confirmation and signup info) prevent a higher confidence rating.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Welcome to the ATL AI Community! Networking &amp; Ecosystem Spotlight presented by TAG Data Science &amp; AI Society</t>
+          <t>AI Education | Beyond the Algorithm: Building the Skills AI Can't Replace</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>July 1, 2026</t>
+          <t>July 1, 2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -819,15 +819,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5:30 PM - 7:30 PM</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>ok</t>
@@ -835,23 +839,23 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>Join technology leaders, founders, practitioners, researchers, investors, students, and community builders for an evening focused on connection, visibility, and conversation around the future of AI in Atlanta.</t>
+          <t>A virtual AI education event focused on building skills that AI cannot replace, hosted by The AI Collective.</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>In-person Georgia AI networking event hosted by TAG (a Georgia institution) with clear AI focus and community-building emphasis, but confidence is medium due to missing venue details and no description of specific educational content.</t>
+          <t>Virtual-only event with clear AI focus and educational value, but hosted by The AI Collective (not a Georgia institution) with insufficient details to determine if it's Georgia-focused or a national offering.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The TAG Fintech Innovation Challenge: Where Are They Now? presented by TAG Fintech Society</t>
+          <t>Brookhaven Monthly Meetup (w/ The AI Collective ATL)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -860,7 +864,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>July 28, 2026</t>
+          <t>July 1, 2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -870,15 +874,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5:30 PM - 7:30 PM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>ok</t>
@@ -886,19 +894,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>A captivating panel discussion where three fintech founders share experiences growing their companies from the ground up.</t>
+          <t>A monthly in-person meetup in Brookhaven, Atlanta, hosted by The AI Collective ATL.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like TAG hosting and in-person format.</t>
+          <t>In-person event in Atlanta hosted by an AI-focused organization (The AI Collective ATL) with clear AI relevance, though the vague description lacks details about content, speakers, or whether it's educational versus social networking.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rural AI Workforce Forum 2026</t>
+          <t>HeyGen is coming to Islamabad!!! | AI Avatar Pop-Up (w/ The AI Collective)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -906,12 +914,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>August 6-7, 2026</t>
+          <t>July 2, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -921,15 +929,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4:00 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>1:00 AM CDT / 11:00 AM GMT+5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Islamabad, Pakistan</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>ok</t>
@@ -937,32 +949,32 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>Preparing rural communities for an AI-driven future.</t>
+          <t>An in-person AI Avatar pop-up event featuring HeyGen, hosted by The AI Collective in Islamabad, Pakistan.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Event mentions AI and is in-person, but critical details are missing (no location specified, making it impossible to determine if it's in Georgia), and the vague description provides insufficient information to assess whether it's educational content or a sales pitch.</t>
+          <t>While the event clearly involves AI (avatar technology) and is in-person, it is located in Islamabad, Pakistan, not Georgia, and appears to be a product demonstration/pop-up that may prioritize promoting HeyGen's services over educational content.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fintech South 2026</t>
+          <t>AI Sandboxes: Giving Developers Room to Experiment Without Giving Up Oversight</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>August 18, 2026</t>
+          <t>July 2, 2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -972,31 +984,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8:00 AM - 7:00 PM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>A virtual event discussing AI sandboxes and how developers can experiment while maintaining oversight, hosted by The AI Collective.</t>
+        </is>
+      </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 score, and the location is unspecified so Georgia presence cannot be confirmed.</t>
+          <t>Virtual-only event with AI content but hosted by The AI Collective (not a Georgia institution), scoring at the lower end of the virtual event range due to lack of Georgia focus.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Atlanta Tech Meet-Up</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1004,12 +1024,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>September 1, 2026</t>
+          <t>July 7, 2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1019,15 +1039,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1035,19 +1059,19 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>Monthly introduction session to TAG membership.</t>
+          <t>Monthly Atlanta Tech Meetup event hosted by Atlanta Tech Meetup group. 92 attendees.</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only membership orientation hosted by Georgia institution (TAG) but lacks any mention of AI/machine learning content, making it primarily an administrative event rather than educational AI content.</t>
+          <t>In-person Georgia event is positive, but no mention of AI, machine learning, or automation content makes it an automatic 1, though the local Atlanta Tech Meetup group and established attendance suggest a slight boost to 2 pending clarification of topics covered.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TAG-Ed 2026 Pathways to Leadership Summit &amp; Graduation</t>
+          <t>From prototype to production with Kiro &amp; Kiro CLI</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1060,7 +1084,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>September 15, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1070,44 +1094,52 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10:00 AM - 3:00 PM</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr"/>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>Event hosted by Atlanta AWS User Group. 20 attendees. Waitlist available.</t>
+        </is>
+      </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Event is hosted by TAG (a Georgia institution) and in-person, which are positive factors, but the complete absence of any mention of AI, machine learning, or automation in the provided details triggers the automatic 1 rating, though being Georgia-based prevents a lower score.</t>
+          <t>While the event is in-person in Georgia and hosted by Atlanta AWS User Group, the description lacks any explicit mention of AI, machine learning, or automation, making it difficult to assess relevance to the criteria.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>//Shift AI 2026</t>
+          <t>Build an Agent Day - Atlanta</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>September 18, 2026</t>
+          <t>July 22, 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1117,15 +1149,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8:00 AM - 3:00 PM</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>8:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1133,23 +1169,23 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>Join us for our kickoff AI Summit Event!</t>
+          <t>Event hosted by All Things AI (Live). 2 attendees.</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>While the event clearly mentions AI and appears to be in-person, the lack of location information (critical for determining if it's in Georgia), missing signup details, and vague description prevent a higher rating.</t>
+          <t>In-person Atlanta event hosted by All Things AI with 'Agent' and 'Build' suggesting hands-on AI/automation content, but limited details about actual AI/ML focus and educational value warrant slightly lower than maximum confidence.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Self-hosting AI on NVIDIA DGX Spark - AI Builders #19: Lunch &amp; Learn</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1158,7 +1194,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>October 6, 2026</t>
+          <t>July 1, 2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1168,15 +1204,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1184,32 +1224,32 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>Monthly introduction session to TAG membership.</t>
+          <t>Lunch &amp; Learn event hosted by ATL BitLab focused on self-hosting AI on NVIDIA DGX Spark. 19 attendees.</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Virtual-only event hosted by Georgia institution (TAG) but lacks any mention of AI/ML/automation content, making it an introductory membership session rather than an educational AI event.</t>
+          <t>In-person Georgia event with clear AI/ML focus (self-hosting AI on NVIDIA hardware) hosted by Atlanta-based BitLab, though the description lacks detail about educational vs. sales-pitch nature.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Annual DataPalooza presented by TAG Data Governance Society</t>
+          <t>Welcome to the ATL AI Community! Networking &amp; Ecosystem Spotlight presented by TAG Data Science &amp; AI Society</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>October 8, 2026</t>
+          <t>July 1, 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1224,7 +1264,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5:30 PM - 7:30 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1233,21 +1273,25 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>Join technology leaders, founders, practitioners, researchers, investors, students, and community builders for an evening focused on connection, visibility, and conversation around the future of AI in Atlanta.</t>
+        </is>
+      </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>TAG is a Georgia institution and DataPalooza suggests an educational data/AI event, but the missing location details, event description, and no explicit mention of AI content prevent a higher score.</t>
+          <t>In-person Atlanta event hosted by TAG (Georgia institution) with explicit AI focus, community networking emphasis, and no sales pitch indicators.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TAG Chairs' Gala 2026</t>
+          <t>The TAG Fintech Innovation Challenge: Where Are They Now? presented by TAG Fintech Society</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1256,7 +1300,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>November 19, 2026</t>
+          <t>July 28, 2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1271,7 +1315,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6:00 PM - 11:00 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1280,28 +1324,36 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr"/>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>A panel discussion where three fintech founders share experiences growing their companies from the ground up.</t>
+        </is>
+      </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>Event details lack any mention of AI, machine learning, or automation, and the description is too vague to assess whether it focuses on these topics.</t>
+          <t>Event is hosted by Georgia-based TAG organization and is in-person, but lacks any mention of AI, machine learning, or automation despite being fintech-focused, triggering the automatic 1 penalty that cannot be fully overcome.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Leading Through the AI Shift: Strategy, Risk &amp; IP</t>
+          <t>Israeli Cybersecurity Summit</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>July 29, 2026</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>June 30, 2026</t>
@@ -1312,21 +1364,1465 @@
           <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rural AI Workforce Forum 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>August 6-7, 2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>Preparing rural communities for an AI-driven future.</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>Event mentions AI and is in-person, but lacks location details (no confirmation it's in Georgia), has minimal description, and no signup link available to assess educational vs. sales-pitch nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fintech South 2026</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>August 18, 2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, and the description is too sparse to determine relevance to AI topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>September 1, 2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>Monthly introductory session to TAG membership.</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>Virtual-only event from Georgia institution (TAG) that lacks any mention of AI, machine learning, or automation content, scoring it as a generic membership orientation rather than educational AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TAG-Ed 2026 Pathways to Leadership Summit &amp; Graduation</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>September 15, 2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>Event is hosted by TAG (a Georgia institution) and in-person in Georgia, but lacks any mention of AI, machine learning, or automation, which is an automatic 1 criterion that cannot be overcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>//Shift AI 2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>September 18, 2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>Kickoff AI Summit Event.</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>Event details are too incomplete to assess (missing location, description lacks AI/ML/automation specifics, and no signup link provided) making it impossible to properly evaluate against the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>October 6, 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>Monthly introductory session to TAG membership.</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>Virtual-only membership orientation by Georgia-based TAG organization lacks AI/ML content focus, though TAG hosting provides modest credibility boost over generic corporate webinars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Annual DataPalooza presented by TAG Data Governance Society</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>October 8, 2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>Event is hosted by TAG (a Georgia institution) and appears to be in-person, but lacks sufficient details about AI/ML content, location confirmation, and description to rate higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026 TAG Invest Connect: Meet, Pitch, &amp; Partner</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>October 22, 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>An annual event that connects Black tech entrepreneurs with the opportunity to pitch to investors looking for innovative ideas.</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>November 3, 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>Monthly introductory session to TAG membership.</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>While hosted by TAG (a Georgia institution), this virtual-only membership orientation lacks any mention of AI, machine learning, or automation content, making it primarily an administrative/onboarding session rather than an educational AI event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>[Pending] Veterans Day presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>November 5, 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifier regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TAG Chairs' Gala 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>November 19, 2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>December 1, 2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>Monthly introductory session to TAG membership.</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>Virtual-only event hosted by Georgia institution (TAG) but lacks any mention of AI/ML/automation content, making it primarily a membership orientation rather than an educational AI event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Leading Through the AI Shift: Strategy, Risk &amp; IP</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>An insightful one-hour program hosted by Taft on navigating the legal and strategic challenges of artificial intelligence in today's business environment.</t>
         </is>
       </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>Virtual-only event with AI content but hosted by Taft (a law firm, not a Georgia institution) with no Georgia focus indicated, making it a generic corporate webinar despite relevant AI topic.</t>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI content but hosted by Taft (a law firm, not a Georgia institution) as what appears to be a service promotion rather than educational content, and missing critical details like date, time, and signup link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Minneapolis Saint Paul AI Tinkerers Meetup</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>July 29, 2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Minneapolis Saint Paul</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>Upcoming AI Tinkerers meetup in Minneapolis Saint Paul.</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>In-person event with clear AI focus, but located in Minneapolis Saint Paul rather than Georgia, which significantly limits its fit according to the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Zürich AI Tinkerers Meetup</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>July 1, 2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>Upcoming AI Tinkerers meetup in Zürich.</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>While the event clearly involves AI and is in-person, it is located in Zürich (not Georgia), and the vague description provides insufficient detail to assess educational value or purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>San Francisco AI Tinkerers Meetup</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>July 8, 2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>Upcoming AI Tinkerers meetup in San Francisco.</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>While the event mentions AI and is in-person, it is located in San Francisco rather than Georgia, which significantly limits its fit according to the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Manchester NH AI Tinkerers Meetup</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>July 22, 2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Manchester, NH</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>Upcoming AI Tinkerers meetup in Manchester, NH.</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>While the event mentions AI and is in-person, it is located in Manchester, NH (not Georgia), and the vague description provides insufficient detail to assess educational value or content quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Atl Greenhouse</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>July 11, 2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Piedmont Park, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>A science &amp; tech event at Piedmont Park in Atlanta, free to attend.</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
+        <is>
+          <t>The event description mentions it is a 'science &amp; tech event' but contains zero explicit mention of AI, machine learning, or automation, triggering the automatic 1 rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>COLLIDE Data + AI Conference 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>October 1, 2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sandy Springs Performing Arts Center, Sandy Springs, Georgia</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>A data and AI conference hosted at the Sandy Springs Performing Arts Center, organized by Data Science Connect.</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr">
+        <is>
+          <t>In-person Georgia event with clear AI/data focus scores highly, but limited details about content quality, whether it's educational vs. sales-focused, and organizer credibility prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI: Strategy. Automation. Growth.</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>July 13, 2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>504 Fair St SW, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>An AI-focused event covering strategy, automation, and growth, organized by Skylar James.</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI focus is favorable, but vague description lacking details about format, speakers, content depth, and whether it's educational or sales-driven prevents a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>InsurTech Atlanta AI at Scale</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>August 11, 2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Serendipity Labs - Buckhead Atlanta, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>An InsurTech event focused on AI at scale, organized by InsurTech Atlanta.</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI focus meets Georgia location criteria well, but limited description details prevent higher confidence on whether it's educational or sales-oriented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>American Modelica and FMI Conference 2026</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>October 12, 2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>275 Ferst Dr NW, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>A technical conference on Modelica and FMI, organized by the Modelica Association and North American Modelica Users' Group.</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t>While this is an in-person event in Atlanta, Modelica and FMI are simulation and modeling standards with no clear mention of AI, machine learning, or automation, making it fail the primary criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>July 3, 2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Fado Irish Pub, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>A recurring tech mixer and social event covering Tech, AI, Data, and IT topics, with 25 more dates available.</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event explicitly mentioning AI/data topics scores well, but the vague description and lack of specific agenda details prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026 Summer STEM Innovation Day</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>July 18, 2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Liberty County Performing Arts Center, Hinesville, Georgia</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>A STEM innovation day event organized by Neuro-Elite, Inc. at the Liberty County Performing Arts Center.</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>The event is in-person in Georgia which is favorable, but the description lacks any mention of AI, machine learning, or automation, triggering an automatic score of 1, though the in-person Georgia location prevents it from being rated lower than 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Marietta, GA (contact info@skelora.com for venue information)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>A 1-day training on strategic prompt design for AI organized by Skelora Edu Tech, with 23 more dates available.</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t>While it is an in-person event in Georgia with AI content, it appears to be a paid training focused on the organizer's core business (Skelora Edu Tech) rather than an educational conference or industry discussion, and the vague description and lack of detailed information suggest it may be a sales-oriented offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Avant South 2026</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>October 12, 2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Tech Square, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>A tech and innovation event held at Tech Square in Atlanta.</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>Event is in-person in Atlanta which is positive, but the description lacks any mention of AI, machine learning, or automation, triggering the automatic 1 penalty, though the in-person Georgia location prevents a lower score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Build an Agent Day - Atlanta</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>July 22, 2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Village - Buckhead, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>A hands-on AI agent building event organized by Mark R. Hinkle at Atlanta Tech Village in Buckhead.</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI/agent-building focus scores highly, but limited event details and no mention of educational content depth or organizer affiliation reduce confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>New AI Tools for Small Business | Expert Webinar</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>July 14, 2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:00 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>A free, interactive webinar with UX designer and AI automator Wonakee Amos covering the newest AI tools for small businesses. Topics include saving time, automating tasks, improving customer experiences, and live Q&amp;A.</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI content but no Georgia focus or hosting institution mentioned, and the small business focus suggests potential sales pitch orientation rather than educational depth.</t>
         </is>
       </c>
     </row>
@@ -1344,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1353,8 +2849,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
@@ -1468,7 +2964,7 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1518,12 +3014,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>A morning networking coffee and connections event in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
+          <t>A morning networking coffee and connections event hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
@@ -1573,12 +3069,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>A networking luncheon in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
+          <t>A networking luncheon for manufacturing professionals hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1633,7 +3129,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which automatically results in a score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1688,7 +3184,7 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 according to the criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of location or format.</t>
         </is>
       </c>
     </row>
@@ -1743,14 +3239,14 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the first criterion.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Plants</t>
+          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Pla...</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1789,12 +3285,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>An event focused on manufacturing technology challenges and practical solutions for today's plants, hosted by the Georgia Manufacturing Alliance.</t>
+          <t>An event focused on manufacturing technology challenges and practical solutions for today's plant operations.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+          <t>The event description makes zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1844,12 +3340,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>A virtual networking event for Women of GMA members.</t>
+          <t>A virtual networking event for Women of GMA (WGMA) members.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1899,12 +3395,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>A morning networking coffee and connections event in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
+          <t>A morning networking coffee and connections event hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of its in-person Georgia location.</t>
         </is>
       </c>
     </row>
@@ -1954,12 +3450,12 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>A networking luncheon in Atlanta hosted by the Georgia Manufacturing Alliance.</t>
+          <t>A networking luncheon for manufacturing professionals hosted by the Georgia Manufacturing Alliance in Atlanta.</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -2009,19 +3505,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>The annual Georgia Manufacturing Summit, a signature event hosted by the Georgia Manufacturing Alliance bringing together manufacturing professionals across the state.</t>
+          <t>The annual Georgia Manufacturing Summit bringing together manufacturing professionals from across the state.</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive criteria.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>FIFA Fan Festival Meetup - July 1st (First Game @ 12pm) - Centennial Olympic Park (w/ The AI Collective)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2034,7 +3530,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>July 6, 2026</t>
+          <t>July 1, 2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2044,15 +3540,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Centennial Olympic Park, Atlanta, GA</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2060,19 +3560,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>A FIFA Fan Festival meetup hosted by The AI Collective at Centennial Olympic Park in Atlanta, GA.</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>While this is an in-person event in Georgia hosted by an AI-focused organization, it is fundamentally a FIFA fan festival with no mention of AI, machine learning, or automation content, triggering the automatic 1 rating.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Criação de imagens e vídeos com inteligência artificial: The AI Collective Florianópolis + Belém Amazônia</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2085,7 +3585,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>July 7, 2026</t>
+          <t>July 1, 2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2095,15 +3595,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2111,19 +3615,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>This 30-minute session is led by Lili Orozco from Member Services, focusing on TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
+          <t>A virtual event on creating images and videos with artificial intelligence, hosted by The AI Collective Florianópolis and Belém Amazônia chapters.</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+          <t>Virtual-only event hosted by non-Georgia organizations (Brazil-based AI Collective chapters) with no Georgia institutional affiliation, making it ineligible for the higher scores reserved for Georgia-focused virtual events.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Superfans and Customer Loyalty: Strategies That Convert Customer Acquisition into Long-Term Advocacy presented by TAG CX Society</t>
+          <t>Open House!</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2136,7 +3640,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 14, 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2146,15 +3650,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3:00 PM - 6:30 PM</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Freeside Atlanta, Georgia</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2162,19 +3670,19 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>This event explores how brands can turn event-driven customer acquisition into long-term loyalty, owned relationships, and measurable customer value.</t>
+          <t>Monthly open house event hosted by Freeside Atlanta. 15 attendees.</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like TAG hosting and in-person format.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IBM SkillsBuild Orientation</t>
+          <t>Find a Startup to Help or Join</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2187,7 +3695,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2197,15 +3705,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6:00 PM - 7:00 PM</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2213,19 +3725,19 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>A mandatory virtual orientation to kick off the upcoming cohort. Participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
+          <t>Monthly event hosted by Projects for Developers and UX Designers. 9 attendees. Cost: $297.00.</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Building Impact Together: A Tech Collaboration &amp; Volunteer Event</t>
+          <t>Python Atlanta Meetup (In Person!)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2238,7 +3750,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>July 17, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2248,31 +3760,39 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10:00 AM - 3:00 PM</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>Monthly in-person Python meetup hosted by PyAtl: Atlanta Python Programmers. 10 attendees.</t>
+        </is>
+      </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 per the criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of its in-person Georgia location.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Summer 2026 Social presented by TAG Digital Health Society</t>
+          <t>🚀 Placeholder Meetup: Stay Tuned for an Exciting Ubuntu TechHive Event!</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2285,7 +3805,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>July 21, 2026</t>
+          <t>July 11, 2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2295,15 +3815,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://members.tagonline.org/calendar</t>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5:30 PM - 7:30 PM</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>10:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2311,19 +3835,19 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>Join TAG's Digital Health Society for an evening of connection and collaboration at their 2026 Summer Social.</t>
+          <t>Placeholder event hosted by The Ubuntu TechHive North America. 3 attendees.</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event description contains no mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or in-person status.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Israeli Cybersecurity Summit</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2336,7 +3860,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>July 29, 2026</t>
+          <t>July 6, 2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2351,7 +3875,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5:00 PM - 8:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2360,17 +3884,21 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>The ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2383,7 +3911,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>August 3, 2026</t>
+          <t>July 7, 2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2398,7 +3926,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>12:30 PM</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2409,19 +3937,19 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>A 30-minute session led by Lili Orozco from Member Services covering TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other factors.</t>
+          <t>The event contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Superfans and Customer Loyalty: Strategies That Convert Customer Acquisition into Long-Term Advocacy presented by TAG CX Society</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2434,7 +3962,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>August 4, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2449,7 +3977,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2460,19 +3988,19 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>This 30-minute session is led by Lili Orozco from Member Services, focusing on TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
+          <t>This event explores how brands can turn event-driven customer acquisition into long-term loyalty, owned relationships, and measurable customer value.</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>The event contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other factors.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>IBM SkillsBuild Orientation</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2485,7 +4013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>September 14, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2500,7 +4028,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2511,19 +4039,19 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>A mandatory virtual orientation to kick off the upcoming cohort. Participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event description contains no mention of AI, machine learning, or automation, triggering the automatic 1 rating per the first criterion.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>Building Impact Together: A Tech Collaboration &amp; Volunteer Event</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2536,7 +4064,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>October 5, 2026</t>
+          <t>July 17, 2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2551,7 +4079,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2560,21 +4088,17 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like being hosted by TAG in Georgia.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026 TAG Invest Connect: Meet, Pitch, &amp; Partner</t>
+          <t>Summer 2026 Social presented by TAG Digital Health Society</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2587,7 +4111,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>October 22, 2026</t>
+          <t>July 21, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2602,7 +4126,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1:00 PM - 5:00 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2613,12 +4137,12 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>TAG Invest Connect is an annual event that connects Black tech entrepreneurs with the opportunity to pitch to investors looking for innovative companies.</t>
+          <t>Join TAG's Digital Health Society for an evening of connection and collaboration at the 2026 Summer Social!</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other positive factors like TAG hosting and in-person format.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +4162,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>November 2, 2026</t>
+          <t>August 3, 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2653,7 +4177,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2664,12 +4188,12 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>The ultimate happy hour experience where connections are made, and fun is had!</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other positive factors like being in-person and hosted by TAG.</t>
+          <t>The event description makes zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive criteria like being hosted by TAG in Georgia.</t>
         </is>
       </c>
     </row>
@@ -2689,7 +4213,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>November 3, 2026</t>
+          <t>August 4, 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2704,7 +4228,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>12:30 PM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2715,19 +4239,19 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>Monthly introduction session to TAG membership.</t>
+          <t>A 30-minute session led by Lili Orozco from Member Services covering TAG's mission and objectives, how to activate your membership, and how to maximize your benefits as a member. Sessions repeat monthly.</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+          <t>The event contains zero mention of AI, machine learning, or automation, which is an automatic disqualifier regardless of other positive factors.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[Pending] Veterans Day presented by TAG Infrastructure Society</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2740,7 +4264,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>November 5, 2026</t>
+          <t>September 14, 2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2755,7 +4279,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11:30 AM - 2:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2764,17 +4288,21 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr"/>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>The ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>Event details contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TAG 101- An Introduction to your TAG Membership</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2787,7 +4315,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>December 1, 2026</t>
+          <t>October 5, 2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2802,7 +4330,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12:30 PM - 1:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2813,19 +4341,19 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>Monthly introduction session to TAG membership.</t>
+          <t>The ultimate happy hour experience where connections are made, and fun is had!</t>
         </is>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 per the criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026 Georgia Day of Code</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2838,7 +4366,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>December 4, 2026</t>
+          <t>November 2, 2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2853,7 +4381,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9:00 AM - 3:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2864,19 +4392,19 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>A free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
+          <t>The ultimate happy hour experience where connections are made, and fun is had!</t>
         </is>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 per the criteria.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Members Only - TAG Converge Series - TAG Hour</t>
+          <t>2026 Georgia Day of Code</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2889,7 +4417,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>December 7, 2026</t>
+          <t>December 4, 2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2904,7 +4432,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5:00 PM - 7:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2915,19 +4443,19 @@
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+          <t>A free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like it being hosted by TAG (a Georgia institution) and in-person.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other factors.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mastercard Small Business Summit</t>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2938,7 +4466,11 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>December 7, 2026</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>June 30, 2026</t>
@@ -2949,7 +4481,11 @@
           <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
@@ -2958,12 +4494,1811 @@
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>Mastercard's third annual Small Business Summit series convening entrepreneurs, financial institutions, local leaders, and industry experts during National Small Business Month with hands-on education, mentorship, and practical resources.</t>
+          <t>The ultimate happy hour experience where connections are made, and fun is had!</t>
         </is>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying criterion.</t>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mastercard Small Business Summit</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>Mastercard's third annual Small Business Summit series convening entrepreneurs, financial institutions, local leaders, and industry experts during National Small Business Month. One-day events delivering hands-on education, mentorship, and practical resources for small businesses.</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cairo AI Tinkerers Meetup</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>July 1, 2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>Upcoming AI Tinkerers meetup in Cairo.</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>Event is in-person but located in Cairo (not Georgia), and the description provides no mention of AI, machine learning, or automation content despite the title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Preparing our Girls for Centerstage : STEAM Summer Camp STEM in Films</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>July 6, 2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>125 Ellis St NE, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>A STEAM summer camp focused on STEM in films for girls, organized by The PAVE Foundation.</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which automatically results in a score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Freshwater Critters</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>July 11, 2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Blue Heron Nature Preserve, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>A nature and science event exploring freshwater critters at the Blue Heron Nature Preserve.</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Next Play: Sports + Tech Experience for Kids &amp; Teens (Ages 6–17)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>July 25, 2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Riverside EpiCenter, Austell, Georgia</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>A sports and tech experience event for kids and teens ages 6–17, organized by Future Tech Leaders.</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Metro Atlanta Science Fair 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>November 12, 2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Lighthouse Preparatory Academy International, Stone Mountain, Georgia</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>A science fair event hosted at Lighthouse Preparatory Academy International in Stone Mountain.</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Women + Tech Meetup</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>July 8, 2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Village, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>A recurring meetup for women in tech, hosted at Atlanta Tech Village with 5 more dates available.</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of other positive factors like in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>God, Science, and Our Search for Meaning</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>August 28, 2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>O. Wayne Rollins Planetarium, Young Harris, Georgia</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>A free event at the O. Wayne Rollins Planetarium exploring the intersection of God, science, and the search for meaning.</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ethical Vulnerability Testing 2-Day Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA (contact info@skelora.com for venue information)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>A 2-day training on ethical vulnerability testing organized by Skelora Edu Tech, with 23 more dates available.</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AWS Solutions Architect Associate Classroom Training in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>July 7, 2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events/?page=1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Gallo Legal Services Savannah, Savannah, Georgia</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>A classroom training course for the AWS Solutions Architect Associate certification, organized by iCertGlobal with 5 more dates available.</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Small Business Morning Collective | Meeting at GEC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>July 1, 2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7:30 AM - 9:00 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>A 90-minute peer-to-peer gathering for small business entrepreneurs to share ideas, network, and discuss business challenges in a comfortable and confidential environment. Free and open to the public; coffee and water provided.</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Small Business Marketing Roundtable with Special Guest Robin Nathaniel</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>July 7, 2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>An interactive discussion about small business marketing basics featuring TEDx speaker and award-winning author Robin Nathaniel. Topics include branding, social media, and campaign planning. Free event with a book giveaway.</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 regardless of other positive factors like in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Visita guiada por el Gwinnett Entrepreneur Center</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>July 14, 2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10:00 AM - 11:00 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>A staff-guided tour of the Gwinnett Entrepreneur Center conducted in Spanish. Small groups walk through the facilities and learn about the Center's benefits, purpose, and mission, with a Q&amp;A opportunity.</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Entrepreneur Center Tour</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>July 14, 2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>11:00 AM - 12:00 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>A one-hour staff-guided tour of the Gwinnett Entrepreneur Center for those interested in learning more about what the Center offers. Conducted in small groups with a Q&amp;A opportunity.</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Small Business Collectives Afternoon Mixer</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>July 15, 2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1:30 PM - 3:00 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046 (GEC)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>A relaxed afternoon mixer for local entrepreneurs featuring light music, refreshments, networking, and an opportunity to meet GEC staff, share business updates, and learn about Center resources. Free registration required.</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Entrepreneur Center Tour</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>July 28, 2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3:00 PM - 4:00 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>A one-hour staff-guided tour of the Gwinnett Entrepreneur Center for those interested in learning more about what the Center offers. Conducted in small groups with a Q&amp;A opportunity.</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Federal Contracts and Teaming: Subcontracting, Joint Ventures, SBA Protégé Program | Bart Njoku-Obi, SBA</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>10:00 AM - 11:30 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Online</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual session with SBA Business Opportunity Specialist Bart Njoku-Obi covering small business opportunities in the federal market, teaming strategies, subcontracting, joint ventures, and the SBA Protégé Program.</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of its in-person Georgia location or other qualities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Small Business Morning Collective at Thrive Suwanee</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>August 5, 2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7:30 AM - 9:00 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Thrive Coworking Suwanee, 500 Buford Highway, Suwanee, GA 30024</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>The monthly Small Business Morning Collective held on the road at Thrive Coworking Suwanee. A 90-minute peer-to-peer gathering for entrepreneurs to share ideas and network. Free and open to the public; coffee and water provided.</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Business Owner Exit Planning: Start with the End in Mind | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual workshop by Edward Jones advisors Joel Barnett and James Herndon on proactive succession and exit planning for business owners, covering how to preserve business value and plan a smooth transition.</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The Lean Startup | Small Business Book Club at Lilburn Library</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12:00 PM - 2:00 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>GCPL Lilburn Branch, 4817 Church St, Lilburn, GA 30047</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>A Small Business Book Club meeting discussing 'The Lean Startup' by Eric Ries. Features a brief book talk, interactive discussion, and open networking. Free, open to any stage of business; reading the book in advance is optional.</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Starting a Business Roundtable</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>August 18, 2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>An interactive roundtable for aspiring and early-stage entrepreneurs covering business planning, funding, licensing, and local support. Facilitated by GEC resident mentor David McCulloch. Free, seating limited; registration opens July 15.</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic 1 score regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Diagnose Your Brand: Is Your Brand Clear or Slowly Drifting?</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>August 20, 2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual workshop with brand strategist Shannel Wheeler focused on evaluating brand perception, identifying inconsistencies, and strengthening brand messaging. Registration opens July 1.</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Exploring Solutions for Workplace Retirement Plans for Small Businesses | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>September 3, 2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual workshop by Edward Jones advisors covering workplace retirement plan options for small business owners, potential tax advantages, and strategies for attracting and retaining employees. Registration opens July 15.</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Exploring SCORE Roundtable</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>September 15, 2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>An interactive roundtable featuring an experienced SCORE mentor discussing how SCORE can help entrepreneurs start and grow a business. Includes a book giveaway. Free, no membership required; registration opens August 15.</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Purposeful Design: Build a Visual System That Supports Your Brand</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>September 17, 2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual workshop with brand strategist Shannel Wheeler on creating a visual brand system to strengthen customer trust, improve marketing materials, and create consistent design guidelines. Registration opens August 1.</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Small Business Legal Topics Roundtable featuring Attorney Ed Campos</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>September 24, 2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>10:00 AM - 11:30 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>A free interactive roundtable with attorney Eduardo Campos covering small business legal topics including company incorporation, contracts, civil and commercial representation, and business compliance. Registration opens September 3.</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>The Power of Budgeting for Entrepreneurs | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>October 1, 2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual interactive workshop by Edward Jones advisors on building and maintaining a budget, distinguishing business wants from needs, and setting practical goals for saving and debt management. Registration opens August 15.</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Small Business Morning Collective at Pinckneyville Community Center</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>October 7, 2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>7:30 AM - 9:00 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Pinckneyville Community Center, 4650 Peachtree Industrial Boulevard, Berkeley Lake, GA 30071</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>The monthly Small Business Morning Collective held on the road at Pinckneyville Community Center. A 90-minute peer-to-peer gathering for entrepreneurs to share ideas and network. Free and open to the public; registration opens September 1.</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Brand Therapy: Live Solutions for Real Brand Challenges</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>October 15, 2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EDT)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual interactive session with brand strategist Shannel Wheeler where participants receive live feedback on their branding challenges and walk away with practical solutions. Registration opens September 1.</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Small Business Marketing Roundtable with Special Guest Robin Nathaniel</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>October 20, 2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>10:00 AM - 11:30 AM (EDT)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>An interactive discussion about small business marketing basics featuring TEDx speaker and award-winning author Robin Nathaniel. Topics include branding, social media, and campaign planning. Free, no membership required; registration opens September 15.</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 according to the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Encore Entrepreneurs Roundtable (50+)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>November 10, 2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EST)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Pinckneyville Recreation Center, 4650 Peachtree Industrial Boulevard, Berkeley Lake, GA 30071</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>A free supportive roundtable discussion for adults 50 and older interested in starting a business. Topics include business planning, funding, licensing, marketing, and local resources. Facilitated by GEC resident mentor David McCulloch. Registration opens October 1.</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of its in-person Georgia location or other merits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>The Social Media System Every Small Business Needs | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>November 12, 2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10:00 AM - 12:00 PM (EST)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC) and Virtual</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>A free in-person and virtual workshop with Ceci Robinson of Robinson Productions covering social media platform selection, real campaign examples, and a step-by-step template to build a streamlined social media system for small businesses. Registration opens October 1.</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Starting a Business Roundtable</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>December 8, 2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>June 30, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:30 PM (EST)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA (GEC)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>An interactive roundtable for aspiring and early-stage entrepreneurs covering business planning, funding, licensing, and local support. Facilitated by GEC resident mentor David McCulloch. Free, seating limited; registration opens November 10.</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
@@ -534,7 +537,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>July 1, 2026</t>
@@ -542,7 +545,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://atlanta.aitinkerers.org/</t>
+          <t>https://luma.com/genai-collective</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -552,8 +555,8 @@
           <t>no_events</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmmm d, yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,7 +52,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -132,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K10" headerRowCount="1">
+  <autoFilter ref="A1:K10"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -152,8 +153,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K1" headerRowCount="1">
-  <autoFilter ref="A1:K1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K12" headerRowCount="1">
+  <autoFilter ref="A1:K12"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -460,18 +461,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -534,29 +535,445 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI: Strategy. Automation. Growth.</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46216</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>July 1, 2026</t>
+          <t>July 2, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://luma.com/genai-collective</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Atlanta · 504 Fair St SW</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>no_events</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI/automation in title scores well, but vague description and missing details (no signup link, no description) prevent higher scoring and create uncertainty about event nature and whether it's educational or a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Build an Agent Day - Atlanta</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI-focused title ('Build an Agent') scores well, but limited details prevent higher confidence assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Atlanta · Fado Irish Pub</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with explicit mention of AI in the title, though the vague description and social mixer format (rather than educational content) prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026 Summer STEM Innovation Day</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hinesville · Liberty County Performing Arts Center</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per the first criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ethical Vulnerability Testing 2-Day Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atlanta, GA · For venue information, Please contact us: info@skelora.com</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Marietta, GA · For venue information, Please contact us: info@skelora.com</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Georgia and mentions AI (prompt design), it appears to be a paid training day that could be a sales pitch for Skelora's services, and the absence of a signup link and description make it difficult to assess educational value versus commercial intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AWS Solutions Architect Associate Classroom Training in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Savannah · Gallo Legal Services Savannah</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person event in Georgia (positive), it appears to be paid AWS certification training rather than an educational AI/ML conference or technical discussion, making it primarily a sales-oriented training course with no clear AI/ML/automation focus mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atlanta · For venue information, Please contact us: info@skelora.com</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Atlanta, the description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Assessment Workshop: Partnering with AI Before the School Year Begins</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atlanta · Mount Vernon School, Upper Campus</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI focus, but limited details about content depth and whether it's educational discussion versus a sales pitch reduce confidence slightly.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -572,17 +989,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
@@ -645,6 +1062,545 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CISSP Certification Training Course in Bothell, CA</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Augusta · 22722 29th Dr SE West, Suite 100, Bothell, WA 98021</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Atl Greenhouse</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Atlanta · Piedmont Park</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Preparing our Girls for Centerstage : STEAM Summer Camp STEM in Films</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Atlanta · 125 Ellis St NE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, making it an automatic 1 per the stated criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Freshwater Critters</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Atlanta · Blue Heron Nature Preserve</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Next Play: Sports + Tech Experience for Kids &amp; Teens (Ages 6–17)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Austell · Riverside EpiCenter</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Women + Tech Meetup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STEM: 1-day Workshop for Students at Wandalands Vineyard &amp; Orchards</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jackson · Wandalands Vineyard and Orchards, LLC</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STEM Family Sundays at iFLY Atlanta!</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atlanta · iFLY Indoor Skydiving - Atlanta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Business Analytics Certification (CBAP) Training in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atlanta · One Glenlake Pkwy NE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Business Analyst (CBAP) Classroom Training in Auburn, AL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Columbus · 5547 Veterans Pkwy</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CBAP® Classroom Training – IIBA® Aligned in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Atlanta · 260 Peachtree St suite 2200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -133,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K10" headerRowCount="1">
-  <autoFilter ref="A1:K10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K54" headerRowCount="1">
+  <autoFilter ref="A1:K54"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -153,8 +153,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K12" headerRowCount="1">
-  <autoFilter ref="A1:K12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K137" headerRowCount="1">
+  <autoFilter ref="A1:K137"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -461,16 +461,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -537,19 +537,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI: Strategy. Automation. Growth.</t>
+          <t>AIMST 2026 – AI Manufacturing &amp; SCADA Technology Conference and Exhibition</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46216</v>
+        <v>46252</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -558,17 +558,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
+          <t>https://www.aimanufacturingconference.com/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atlanta · 504 Fair St SW</t>
+          <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -576,21 +572,25 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>North America's #1 Conference in Industrial AI, focused on providing in-depth discussions and solutions for heads of manufacturing, advanced technology managers, ICS, IT/OT, SCADA and cyber security professionals to accelerate digital transformation and transform operational and automation systems. Features 60+ speakers, 350+ attendees, three tech tracks, and 8+ networking events.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>In-person Atlanta event with AI/automation in title scores well, but vague description and missing details (no signup link, no description) prevent higher scoring and create uncertainty about event nature and whether it's educational or a sales pitch.</t>
+          <t>This is an in-person, multi-day industrial AI conference in Atlanta with substantial educational content (60+ speakers, 350+ attendees, multiple tracks) that fits all top-scoring criteria.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Build an Agent Day - Atlanta</t>
+          <t>SCL Course: Machine Learning Applications for Supply Chain Planning (Virtual/Instructor-Lead)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46225</v>
+        <v>46279</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -607,17 +607,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>1:00 PM EDT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+          <t>Virtual/Instructor-led</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,21 +625,25 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Apply machine learning with Python and Power BI to optimize supply chain forecasting, inventory, and maintenance.</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>In-person Atlanta event with AI-focused title ('Build an Agent') scores well, but limited details prevent higher confidence assessment.</t>
+          <t>Virtual-only paid training course with machine learning content but no Georgia focus or hosting by Georgia institution, appears to be a commercial training offering rather than educational discussion.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+          <t>SCL Course: Generative AI Application for Supply Chain Professionals (Virtual/Instructor-led)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -647,7 +651,7 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46206</v>
+        <v>46496</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -656,17 +660,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>8:00 PM EDT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Atlanta · Fado Irish Pub</t>
+          <t>Virtual/Instructor-led</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -674,29 +678,33 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Participants will explore generative AI fundamentals, prompt engineering, and practical applications such as automated inventory systems, predictive maintenance, and route optimization.</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>In-person Atlanta event with explicit mention of AI in the title, though the vague description and social mixer format (rather than educational content) prevent a perfect score.</t>
+          <t>Virtual-only event with clear AI/generative AI focus and practical supply chain applications, but lacks Georgia institution affiliation or Georgia-specific focus, and appears to be a paid training course rather than educational discussion or conference.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026 Summer STEM Innovation Day</t>
+          <t>SCL Course: Generative AI Application for Supply Chain Professionals (Onsite/In-Person)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46221</v>
+        <v>46678</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,17 +713,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>8:00 PM EDT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hinesville · Liberty County Performing Arts Center</t>
+          <t>Georgia Tech Savannah</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -723,29 +731,35 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Participants will explore generative AI fundamentals, prompt engineering, and practical applications such as automated inventory systems, predictive maintenance, and route optimization.</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per the first criterion.</t>
+          <t>In-person Georgia Tech event with clear AI/ML focus on generative AI applications, though the paid training format and supply-chain-specific angle prevent a higher score.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ethical Vulnerability Testing 2-Day Training in Atlanta, GA</t>
+          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46205</v>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>August 18, 2026 - August 20, 2026</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -754,19 +768,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Atlanta, GA · For venue information, Please contact us: info@skelora.com</t>
-        </is>
-      </c>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>ok</t>
@@ -775,26 +781,26 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of being in-person in Georgia.</t>
+          <t>While the event is in-person and AI-focused, critical details are missing (location, description) making it impossible to confirm if it's Georgia-based, and the vague details prevent a higher rating.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -803,47 +809,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Marietta, GA · For venue information, Please contact us: info@skelora.com</t>
-        </is>
-      </c>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>This 30-minute session is led by Lili Orozco from Member Services. This session will focus on the following topics: TAG's mission and objectives, how to activate your membership, how to maximize your benefits as a member. Sessions repeat monthly.</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>While the event is in-person in Georgia and mentions AI (prompt design), it appears to be a paid training day that could be a sales pitch for Skelora's services, and the absence of a signup link and description make it difficult to assess educational value versus commercial intent.</t>
+          <t>Virtual event hosted by Georgia-focused institution (TAG) with membership orientation focus, but lacks specific AI/ML/automation content mention despite TAG's AI industry focus.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect Associate Classroom Training in Savannah, GA</t>
+          <t>Israeli Cybersecurity Summit</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -852,19 +858,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Savannah · Gallo Legal Services Savannah</t>
-        </is>
-      </c>
+          <t>5:00 PM - 8:00 PM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>ok</t>
@@ -873,18 +875,18 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>While this is an in-person event in Georgia (positive), it appears to be paid AWS certification training rather than an educational AI/ML conference or technical discussion, making it primarily a sales-oriented training course with no clear AI/ML/automation focus mentioned.</t>
+          <t>Event details are too sparse to evaluate properly, but the title and lack of location/description suggest this is likely a cybersecurity event without clear mention of AI, machine learning, or automation, and the empty fields make assessment uncertain.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -892,7 +894,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46220</v>
+        <v>46238</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -901,77 +903,2235 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Atlanta · For venue information, Please contact us: info@skelora.com</t>
-        </is>
-      </c>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>This 30-minute session is led by Lili Orozco from Member Services. This session will focus on the following topics: TAG's mission and objectives, how to activate your membership, how to maximize your benefits as a member. Sessions repeat monthly.</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>While the event is in-person in Atlanta, the description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating.</t>
+          <t>Virtual event hosted by TAG (a Georgia institution) with membership orientation focus, but lacks explicit AI/ML/automation content which is required and would elevate the score.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Rural AI Workforce Forum 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>August 6-7, 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4:00 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Preparing rural communities for an AI-driven future.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI focus and educational merit, but lacks confirmation of Georgia institutional hosting or Georgia-specific focus, and critical details (location, signup link, host organization) are missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fintech South 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8:00 AM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Event details are too incomplete to assess (no description, location, or link provided), and without confirmation of AI/ML content, it defaults to automatic 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TAG-Ed 2026 Pathways to Leadership Summit &amp; Graduation</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10:00 AM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event hosted by TAG (Georgia-focused organization) scores in the 3-4 range per criteria, but incomplete event details (missing description, location info) prevent higher confidence and potentially higher scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>//Shift AI 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8:00 AM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Join us for our kickoff AI Summit Event!</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with mentions of AI in title, but lacks location details, signup information, and sufficient context to determine if it's Georgia-focused or a national corporate event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Annual DataPalooza presented by TAG Data Governance Society</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>DataPalooza returns in 2026, bringing together Atlanta's data governance, privacy, and data management leaders for an evening of meaningful connection.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person Atlanta event by TAG (a Georgia institution), the description contains zero explicit mention of AI, machine learning, or automation, triggering the automatic 1 rule, though the data governance focus suggests relevance that prevents a true 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>[Pending] Veterans Day presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46331</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>11:30 AM - 2:00 PM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Event details contain zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the first criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TAG Chairs' Gala 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46345</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6:00 PM - 11:00 PM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Event details are too sparse to assess content, but the title suggests a social gala rather than an educational AI event, and there is no mention of AI, machine learning, or automation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026 Georgia Day of Code</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46360</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>9:00 AM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026 Georgia Day of Code is a free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with Georgia focus and free educational coding content, but lacks explicit mention of AI/ML/automation which would elevate the score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>From prototype to production with Kiro &amp; Kiro CLI</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains no mention of AI, machine learning, or automation, which is an automatic disqualifying criterion regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bytes &amp; Bites @ Krog St Market</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Krog St Market, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 score despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DC470 Meetup</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AWS: Build Resilient Multi-Step Applications With Just Code</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with technical AWS content, but lacks clear mention of AI/ML/automation focus and appears to be a corporate product demo rather than educational, making it difficult to assess against the AI criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GA AI Alliance Networking Lunch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>In-person Georgia event with AI focus (GA AI Alliance suggests strong AI relevance), but lacks detail on content depth and whether it's educational or purely social networking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q&amp;AI Weekly — Build Real AI Skills (Live with Bobby V.)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>The event description is too vague to confirm AI/ML content involvement, and the minimal details provided cannot establish whether it meets educational or Georgia-focused criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Build an Agent Day - Atlanta</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI/agent-building focus scores highly, but limited details about educational value versus sales pitch nature create moderate confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Meet + Greet + Discuss + Build</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 score despite being in-person in Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Escape the 9–5 Live | NO B.S. AI with Bobby</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Event details are too vague to confirm AI/ML/automation content, and the empty short_description combined with a virtual-only format without Georgia institutional affiliation suggests it cannot meet the AI criteria threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ship It Sundays: July 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Georgia Day of Action</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation, triggering automatic minimum score regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI That Remembers You: A Beginner's Guide to Memory Systems</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI/machine learning focus (memory systems) scores highly, but incomplete event details and unknown organizer/format limit confidence that it's educational rather than a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>How to Use AI for Academic Research</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>9:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI topic but no indication of Georgia focus or hosting institution, and minimal details provided to assess educational value versus sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Sandboxes: Giving Developers Room to Experiment Without Giving Up Oversight</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI focus and educational merit (technical topic about AI sandboxes and developer oversight), but is virtual-only with no indication of Georgia focus or Georgia institution hosting, and lacks sufficient details to confirm it's not a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The Copilot Effect: Github Copilot (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Event clearly mentions AI (GitHub Copilot) but is virtual-only with no indication of Georgia focus or Georgia institution hosting, though minimal details prevent higher confidence assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AIC FXBG Presents: Using AI to Improve</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Event details are too incomplete to assess (missing location, description, and signup information), and there is no explicit mention of AI, machine learning, or automation in the provided information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IA, Cultura e Clima (w/ The AI Collective) (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Event details are incomplete with no description provided, making it impossible to verify AI/ML/automation content, and the virtual-only format on Google Meet with no Georgia institutional affiliation scores poorly by default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Achieving Escape Velocity - Demo Night @ Florida Atlantic</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Florida Atlantic University</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Human Agency in Decision-Making with AI (w/ The AI Collective ATL)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI focus on decision-making, hosted by a local AI collective, though limited details prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sandy Springs AI Meetup (w/ The AI Collective ATL)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>In-person Georgia event (Sandy Springs) with clear AI focus through The AI Collective ATL organization, though the minimal event details provided prevent a higher confidence rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI HR Roundtable with The AI Collective KC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI mention but no indication of Georgia focus or host institution, and insufficient details to assess educational value versus sales pitch nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>The Copilot Effect: Microsoft Fabric Copilot (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only national corporate event from Microsoft with no Georgia focus or institution affiliation, and insufficient event details to assess educational value versus sales pitch nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The Copilot Effect: Power Platform Copilot (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>While the event title mentions AI/Copilot, the virtual-only format combined with insufficient details about Georgia focus, organizer affiliation, or educational value, plus the unclear nature of what appears to be a Microsoft product promotion, cannot overcome the lack of concrete information to rate higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI: Strategy. Automation. Growth.</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Atlanta · 504 Fair St SW</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI/automation focus scores well, but extremely vague description and missing details make it difficult to assess whether it's educational, a sales pitch, or otherwise substantive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Build an Agent Day - Atlanta</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with 'Agent' (AI-related) in the title scores well, but lacks detail about content, duration, and whether it's educational or sales-focused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Atlanta · Fado Irish Pub</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI/data focus is a strong fit, but the vague description and lack of details about content depth or educational value prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ethical Vulnerability Testing 2-Day Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Atlanta, there is zero mention of AI, machine learning, or automation, which is an automatic disqualifier regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Marietta, GA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Georgia (positive) and mentions AI prompt design, the minimal details and lack of description suggest it may be a paid training/sales pitch rather than an educational conference, and the absence of substantive information prevents higher confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AWS Solutions Architect Associate Classroom Training in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Savannah · Gallo Legal Services Savannah</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person event in Georgia, it appears to be paid AWS certification training (a sales pitch for AWS services) rather than an educational discussion about AI/automation, and lacks any clear mention of AI content despite AWS involving cloud services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Atlanta (positive) but lacks any mention of AI, machine learning, or automation in title or description, triggering the automatic 1 rating, though location prevents it from being strictly 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>AI Assessment Workshop: Partnering with AI Before the School Year Begins</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D49" s="1" t="n">
         <v>46233</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>July 2, 2026</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Atlanta · Mount Vernon School, Upper Campus</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>In-person event in Atlanta with clear AI focus, but limited details about content depth and whether it's educational discussion versus a sales pitch reduce confidence slightly.</t>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with explicit AI focus that appears educational for school staff, though limited details prevent higher confidence and the workshop nature suggests it may include some sales component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>New AI Tools for Small Business | Expert Webinar</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Join UX designer, funnel builder, and AI automator Wonakee Amos for a practical, highly interactive look at the newest AI tools helping small businesses save time, improve customer experiences, and work more efficiently. The webinar will cut through the hype, highlight which tools are actually worth your time, and include live Q&amp;A and discussion throughout the session.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI/automation content but no Georgia institutional affiliation, appears to be a general webinar that could be a sales pitch for the presenter's services rather than educational content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI Builders #20: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>A Lunch &amp; Learn covering a wide range of AI topics: the latest cool AI tools, integrating AIs into projects via APIs, and customizing agents and models. No useless philosophizing—only straight-up real AI talk. Bring your own sack lunch or DoorDash something to the Lab. All skill levels welcome.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>In-person educational AI event in Atlanta covering practical AI topics (tools, APIs, agents, models) with inclusive messaging and no apparent sales pitch, fitting the criteria for a strong Georgia-based AI event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>The AI Underground - Conference</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>9:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>A conference for people building the future of freedom with AI. From open weight models to open source agents, the AI Underground brings together the minds building AI into a technology of liberation.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference in Atlanta, Georgia with clear focus on AI/open source technologies and no apparent sales pitch orientation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Builders #21: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>A Lunch &amp; Learn covering a wide range of AI topics: the latest cool AI tools, integrating AIs into projects via APIs, and customizing agents and models. No useless philosophizing—only straight-up real AI talk. Bring your own sack lunch or DoorDash something to the Lab. All skill levels welcome.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI/technical focus, educational format, and practical content (tools, APIs, agents) rather than a sales pitch, though lacking specific speaker/organizer details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI Builders #22: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>A Lunch &amp; Learn covering a wide range of AI topics: the latest cool AI tools, integrating AIs into projects via APIs, and customizing agents and models. No useless philosophizing—only straight-up real AI talk. Bring your own sack lunch or DoorDash something to the Lab. All skill levels welcome.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI focus covering practical topics (APIs, agents, models) that aligns well with educational AI discussion criteria, though limited details prevent a perfect score.</t>
         </is>
       </c>
     </row>
@@ -989,7 +3149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -998,7 +3158,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -1065,7 +3225,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CISSP Certification Training Course in Bothell, CA</t>
+          <t>Roper Factory Tour - LaFayette</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1077,7 +3237,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46230</v>
+        <v>46211</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1086,17 +3246,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9:00 AM - 11:30 AM EDT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augusta · 22722 29th Dr SE West, Suite 100, Bothell, WA 98021</t>
+          <t>LaFayette, Georgia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1107,14 +3267,14 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Atl Greenhouse</t>
+          <t>Coffee and Connections - Atlanta 7-16-2026</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1126,7 +3286,7 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46214</v>
+        <v>46219</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1135,17 +3295,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>8:30 AM - 10:00 AM EDT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Atlanta · Piedmont Park</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1163,7 +3323,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Preparing our Girls for Centerstage : STEAM Summer Camp STEM in Films</t>
+          <t>Networking Luncheon - Atlanta 7-16-2026</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1175,7 +3335,7 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1184,17 +3344,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>11:30 AM - 1:00 PM EDT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Atlanta · 125 Ellis St NE</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1205,14 +3365,14 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, making it an automatic 1 per the stated criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per the primary criterion.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Freshwater Critters</t>
+          <t>WGMA Paint the Town - The Davis Companies</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1224,7 +3384,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46214</v>
+        <v>46225</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1233,19 +3393,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Atlanta · Blue Heron Nature Preserve</t>
-        </is>
-      </c>
+          <t>11:00 AM - 1:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1254,14 +3410,14 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Next Play: Sports + Tech Experience for Kids &amp; Teens (Ages 6–17)</t>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1273,7 +3429,7 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46228</v>
+        <v>46233</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1282,17 +3438,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>9:00 AM - 12:00 PM EDT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Austell · Riverside EpiCenter</t>
+          <t>Gainesville, Georgia</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1303,14 +3459,14 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other factors.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which automatically results in a score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Women + Tech Meetup</t>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville - AFTERNOON</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1322,7 +3478,7 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46211</v>
+        <v>46233</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1331,17 +3487,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>11:30 AM - 4:00 PM EDT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Atlanta · Atlanta Tech Village</t>
+          <t>Gainesville, Georgia</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1352,14 +3508,14 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or format.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STEM: 1-day Workshop for Students at Wandalands Vineyard &amp; Orchards</t>
+          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Plant</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1371,7 +3527,7 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46221</v>
+        <v>46239</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1380,19 +3536,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Jackson · Wandalands Vineyard and Orchards, LLC</t>
-        </is>
-      </c>
+          <t>11:00 AM - 1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1401,14 +3553,14 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+          <t>The event details contain zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STEM Family Sundays at iFLY Atlanta!</t>
+          <t>Women of GMA Virtual Networking Event 8/11/26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1420,7 +3572,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46215</v>
+        <v>46245</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1429,19 +3581,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Atlanta · iFLY Indoor Skydiving - Atlanta</t>
-        </is>
-      </c>
+          <t>3:30 PM - 4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1450,14 +3598,14 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which automatically results in a score of 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Business Analytics Certification (CBAP) Training in Sandy Springs, GA</t>
+          <t>Coffee and Connections - Atlanta 8-20-2026</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1469,7 +3617,7 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1478,17 +3626,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>8:30 AM - 10:00 AM EDT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Atlanta · One Glenlake Pkwy NE</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1499,14 +3647,14 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic 1 rating regardless of other criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Business Analyst (CBAP) Classroom Training in Auburn, AL</t>
+          <t>Networking Luncheon - Atlanta 8-20-2026</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1518,7 +3666,7 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1527,17 +3675,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>11:30 AM - 1:00 PM EDT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Columbus · 5547 Veterans Pkwy</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1548,14 +3696,14 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CBAP® Classroom Training – IIBA® Aligned in Atlanta, GA</t>
+          <t>2026 Georgia Manufacturing Summit</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1567,7 +3715,7 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46224</v>
+        <v>46280</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1576,17 +3724,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>7:00 AM - 4:00 PM EDT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Atlanta · 260 Peachtree St suite 2200</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1597,7 +3745,6264 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Superfans and Customer Loyalty: Strategies That Convert Customer Acquisition into Long-Term Advocacy presented by TAG CX Society</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3:00 PM - 6:30 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>This event explores how brands can turn event-driven customer acquisition into long-term loyalty, owned relationships, and measurable customer value.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IBM SkillsBuild Orientation</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and demo on how to access the learning platform.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Building Impact Together: A Tech Collaboration &amp; Volunteer Event</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10:00 AM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualifying criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Summer 2026 Social presented by TAG Digital Health Society</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Join TAG's Digital Health Society for an evening of connection and collaboration at our 2026 Summer Social!</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The TAG Fintech Innovation Challenge: Where Are They Now? presented by TAG Fintech Society</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a captivating panel discussion as three fintech founders share experiences growing their companies from the ground up.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026 TAG Invest Connect: Meet, Pitch, &amp; Partner</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1:00 PM - 5:00 PM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>TAG INVEST CONNECT is an annual event that connects Black tech entrepreneurs with the opportunity to pitch to investors looking for innovative ideas.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46328</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46329</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of TAG being a Georgia institution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>12:30 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46363</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Meet-Up</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Find a Startup to Help or Join</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Python Atlanta Meetup (In Person!)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Civic Action Night at Tech Square ATL (TSQATL) Social Club</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Tech Square ATL, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bitcoin Prophecy: What Argentina Can Teach You About Your Money</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>🚀 Placeholder Meetup: Stay Tuned for an Exciting Ubuntu TechHive Event!</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Event details are a placeholder with no description, no location specified, no signup link, and zero mention of AI, machine learning, or automation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Happy Birthday OWASP! 25 Year Anniversary Party</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Monthly 2600 Meeting!</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>🚀 Placeholder Meetup: Stay Tuned for an Exciting Ubuntu TechHive Event!</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>10:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Event details are a placeholder with no mention of AI, machine learning, or automation, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Nostr Atlanta #14 - Decentralized Web Tech - Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Microsoft DP-600 Certification Study Group - Session 4</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation (it is a Microsoft certification study group focused on DP-600, which is a data platform certification unrelated to AI), triggering the automatic 1 rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>🎬☕ Write Once. Run Forever: The Java Story – AJUG Watch Party</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6:45 PM EDT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>The Calculi of Lambda-Conversion, presented by Nandu Shah</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #52</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Monitoring the Situation: Bitcoin News Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Monthly Meetup + Game Night: July 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Plugin Security Without the Panic: Staying Safe When WordPress Risks Move Faster</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Gwinnett, Georgia</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #1</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI + Breakfast in Etobicoke (w/ The AI Collective)_🇨🇦 Canada Day Special:</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>6:30 AM</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Canada, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MakeAlong: Build an AI agent you can trust (w/ The AI Collective Mumbai)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>12:30 AM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Mumbai, India</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Location is in India, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Build with Qwen (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1:30 AM</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Nairobi, Kenya</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Kenya, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>From Spreadsheets to AI: The Next Era of Financial Analysis (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>6:00 AM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Islamabad, Pakistan</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Pakistan, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>An Evening at the Frontier of AI</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Hildale, UT</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Utah (UT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>You're Building the AI Boom. Do You Own Any of It?</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>6:00 AM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Malaysia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Visionary Diagnostics: Products Advancing Diagnostic Capabilities</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Levallois-Perret, France</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Location is in France, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Demo Night 6 | Stamford AI Meetup | (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AI Brunch (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3:00 AM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Wien, Austria</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Austria, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Governance for SMEs: Practical Solutions (without the Enterprise headache) w/ The AI Collective</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>5:30 AM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Singapore, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IA en Venezuela: del hype a la adopción real</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Caracas, Venezuela</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Venezuela, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Vibin' Out (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Shippan Landing, 262 Harbor Dr 1st Floor, Stamford, CT 06902</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Founder Fridays: The AI Collective x Unstuck Labs</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Building an AI Agent with Make.com x AI Collective</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3:30 AM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Location is in India, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Boston)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Massachusetts (MA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Automatizaciones + IA: el futuro del trabajo manual (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Argentina, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Applied AI innovation Night (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Spain, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Miami)</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Florida (FL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Founder Fridays: The AI Collective x Unstuck Labs</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HeyGen is coming to Islamabad!!! | AI Avatar Pop-Up (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1:00 AM</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Islamabad, Pakistan</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Pakistan, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AI and the Future of Work (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Manassas, VA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Pioneer Day: A Pie &amp; Beer Mixer</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>South Salt Lake, UT</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Utah (UT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Building with AI: Open Mic Night (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Founder Fridays: The AI Collective x Unstuck Labs</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI Demo Night: AWS x AI Collective</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C-Suite Dinner: The Full Arc of Operationalising AI (w/ FACCI &amp; The AI Collective) - FOLLOW LINK BELOW FOR TICKET</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>3:00 AM</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Adelaide, Australia</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Australia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Space Coast AI Town Hall</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Cocoa, FL</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Florida (FL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SF DEMO NIGHT 🚀 (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (San Francisco)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Chicago)</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Illinois (IL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Austin)</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Portland)</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Oregon (OR), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Toronto)</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Canada, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Vibe Night in Midtown (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its description, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SUMMER BREAK - ENJOY AI-FREE TIME IN THE COTTAGE!</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the first criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>🧠 The AI Collective Netherlands | September Meetup (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Event is in the Netherlands (not Georgia), lacks any mention of AI/machine learning/automation in the description, and has insufficient details to determine educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Atl Greenhouse</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Atlanta · Piedmont Park</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualification per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Preparing our Girls for Centerstage : STEAM Summer Camp STEM in Films</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Atlanta · 125 Ellis St NE</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Freshwater Critters</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Atlanta · Blue Heron Nature Preserve</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Next Play: Sports + Tech Experience for Kids &amp; Teens (Ages 6–17)</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Austell · Riverside EpiCenter</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Women + Tech Meetup</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026 Summer STEM Innovation Day</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Hinesville · Liberty County Performing Arts Center</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STEM: 1-day Workshop for Students at Wandalands Vineyard &amp; Orchards</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Jackson · Wandalands Vineyard and Orchards, LLC</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STEM Family Sundays at iFLY Atlanta!</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Atlanta · iFLY Indoor Skydiving - Atlanta</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Business Analytics Certification (CBAP) Training in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Atlanta · One Glenlake Pkwy NE</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CBAP® Classroom Training – IIBA® Aligned in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Atlanta · 260 Peachtree St suite 2200</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Small Business Marketing Roundtable with Special Guest Robin Nathaniel</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Join fellow entrepreneurs for an interactive discussion about small business marketing basics: what's working, what's not, and what's next. Facilitated by a Gwinnett Entrepreneur Center staff member, with special guest Robin Nathaniel, TEDx speaker and award-winning author &amp; marketing strategist. Includes a book giveaway of The One Page Marketing Plan by Allan Dib.</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Visita guiada por el Gwinnett Entrepreneur Center</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Visita guiada en español por las instalaciones del Centro en grupos reducidos, acompañado por un miembro del equipo. Este recorrido de una hora ofrece una visión directa de los beneficios, el propósito y la misión del Centro, así como la oportunidad de plantear preguntas y recibir respuestas.</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Entrepreneur Center Tour</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Staff-guided scheduled tour walking visitors through in small groups. This one-hour tour offers direct insight into the benefits, purpose and mission of the Center as well as an opportunity for questions and answers.</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Small Business Collectives Afternoon Mixer</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>A relaxed and engaging afternoon mixer designed to bring local entrepreneurs together in a fun, welcoming environment. Enjoy light music, light refreshments, and a casual atmosphere. Connect with fellow small business owners, meet the Center Manager and staff, share what you're working on, and learn more about opportunities and resources available at the Center.</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualifying criterion regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Entrepreneur Center Tour</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>405 North Perry Street, Lawrenceville, GA 30046</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Staff-guided scheduled tour walking visitors through in small groups. This one-hour tour offers direct insight into the benefits, purpose and mission of the Center as well as an opportunity for questions and answers.</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the scoring criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Federal Contracts and Teaming: Subcontracting, Joint Ventures, SBA Protégé Program</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Online</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>With Bart Njoku-Obi, Business Opportunity Specialist, US SBA Georgia District Office. Learn the latest about the opportunity landscape for small business in the federal market, understand different approaches to teaming, learn strategies for identifying teaming opportunities or prospective partners, and discover local resources available to help you get started.</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>The event contains zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Small Business Morning Collective at Thrive Suwanee</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>7:30 AM</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Thrive Coworking Suwannee, 500 Buford Highway, Suwanee, GA 30024</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>The GEC Small Business Collectives provide a comfortable and confidential environment for small business entrepreneurs to share ideas and discuss the challenges of business. These peer-to-peer gatherings last for 90 minutes, providing a convenient opportunity for busy individuals to come together, network, and collaborate. Coffee &amp; water provided.</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Business Owner Exit Planning: Start with the End in Mind | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>This session highlights the importance of taking a proactive and intentional approach to succession and exit planning. It covers key steps business owners can begin implementing now to help ensure a smooth and successful transition on their own terms. Presented by Joel Barnett and James Herndon of Edward Jones.</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>The event contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>The Lean Startup | Small Business Book Club at Lilburn Library</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>GCPL Lilburn Branch, 4817 Church St, Lilburn, GA 30047</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Book club discussion of The Lean Startup: How Today's Entrepreneurs Use Continuous Innovation To Create Radically Successful Businesses by Eric Ries. Opens with a brief book talk followed by interactive discussion. Please stay after for open networking time. Free registration, open to any stage of business — read the book or just listen in.</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person Georgia event, it has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Starting a Business Roundtable</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Join aspiring and early-stage entrepreneurs for an interactive discussion about what it really takes to start a business. Facilitated by the Gwinnett Entrepreneur Center resident mentor, this is a space to share ideas, ask questions, and explore key topics like business planning, funding, licensing, and local support programs. Registration opens July 15.</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Diagnose Your Brand: Is Your Brand Clear or Slowly Drifting?</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>In this practical workshop with brand strategist Shannel Wheeler, you'll evaluate how your business is currently perceived, identify inconsistencies, and uncover opportunities to strengthen your brand message so customers clearly understand who you are and why they should choose you.</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Exploring Solutions for Workplace Retirement Plans for Small Businesses | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>This workshop provides an overview of workplace retirement plan options available to business owners and their employees. Presented by Joel Barnett and James Herndon of Edward Jones. Registration opens July 15.</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Exploring SCORE Roundtable</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Join entrepreneurs and small business owners for an interactive discussion about how SCORE can help you start, manage, and grow your business. Features insights from an experienced SCORE mentor. Learn how to connect with a mentor, access free resources, and make the most of this powerful network of business support. Registration opens August 15.</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Purposeful Design: Build a Visual System That Supports Your Brand</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>In this practical workshop with Shannel Wheeler, you'll learn how to create a visual system that aligns with your brand, strengthens customer trust, and makes your marketing more effective. Develop a purposeful approach that supports your business goals and creates a more consistent customer experience. Registration opens August 1.</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Small Business Legal Topics Roundtable</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>An interactive roundtable featuring attorney Eduardo Campos, J.D., M.P.A. Designed for entrepreneurs and small business owners who want to better understand legal considerations impacting their businesses. Topics may include company incorporation, contracts &amp; agreements, civil &amp; commercial representation, and business compliance. Registration opens September 3.</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>The event contains zero mention of AI, machine learning, or automation, which is an automatic disqualifying factor regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>The Power of Budgeting for Entrepreneurs | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>This interactive session focuses on building and maintaining a budget, distinguishing between business wants and needs, and setting practical goals for personal spending, saving, and debt management. Presented by Joel Barnett and James Herndon of Edward Jones. Registration opens August 15.</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Small Business Morning Collective at Pinckneyville Community Center</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>7:30 AM</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Pinckneyville Community Center, 4650 Peachtree Industrial Boulevard, Berkeley Lake, GA 30071</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>The GEC Small Business Collectives provide a comfortable and confidential environment for small business entrepreneurs to share ideas and discuss the challenges of business. These peer-to-peer gatherings last for 90 minutes. Registration is free, open to the public. Coffee &amp; water provided. Registration opens September 1.</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Brand Therapy: Live Solutions for Real Brand Challenges</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Bring your questions, challenges, and brand frustrations to this interactive session with Shannel Wheeler. Participants will have the opportunity to receive live feedback, discuss real-world branding issues, and walk away with practical solutions they can immediately apply to strengthen their business presence. Registration opens September 1.</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria regardless of its in-person Georgia location or other qualities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Small Business Marketing Roundtable</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Join fellow entrepreneurs for an interactive discussion about small business marketing basics: what's working, what's not, and what's next, with special guest Robin Nathaniel, TEDx speaker and award-winning author &amp; marketing strategist. A space to share ideas, get feedback, and learn practical ways to promote your business more effectively. Registration opens September 15.</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Encore Entrepreneurs Roundtable (50+)</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>46336</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Pinckneyville Recreation Center, 4650 Peachtree Industrial Boulevard, Berkeley Lake, GA 30071</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Join fellow adults 50 and up for an engaging and supportive roundtable discussion focused on starting a business in your next chapter. Whether pursuing a long-time dream, turning a hobby into income, or exploring a new purpose after retirement or career transition, this session offers practical guidance and real conversation about what it takes to launch successfully. Registration opens October 1.</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>The Social Media System Every Small Business Needs | Expert Workshop</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>46338</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville and Virtual</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>With Ceci Robinson, founder of Robinson Productions. Learn techniques that keep social media running while you stay focused on strategy and growth. Covers top social media platforms, real campaign examples, and includes a step-by-step template. No big budget required — just a clear system that streamlines your social media. Registration opens October 1.</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>The event contains zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Starting a Business Roundtable</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>46364</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://gec1.wildapricot.org/events</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>GEC 405 North Perry Street, Lawrenceville</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Join aspiring and early-stage entrepreneurs for an interactive discussion about what it really takes to start a business. Facilitated by the Gwinnett Entrepreneur Center resident mentor, this is a space to share ideas, ask questions, and explore key topics like business planning, funding, licensing, and local support programs. Registration opens November 10.</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Bitcoin Prophecy: What Argentina Can Teach You About Your Money</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>A conversation with Ariel Aguilar, author of 'Bitcoin Prophecy: What Argentina Can Teach You About Your Money', who draws on lived experience of one of the world's highest inflation rates—devaluations, deposit confiscations, and exchange controls—to argue for Bitcoin as a way out of broken monetary systems. Ariel has driven two Bitcoin vans across Argentina and 20 European countries, organizing meetups and conferences over 60,000+ miles.</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Nostr Atlanta #14 - Decentralized Web Tech - Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>A Lunch &amp; Learn for nostr users, content creators, enthusiasts, and developers. Either bring a bag lunch or do a DoorDash together. Nostr is a censorship-resistant social media protocol that flips the current internet paradigm using relays and public-key cryptography to empower users to control their own data.</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #52</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs every third Wednesday for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning. Events are formatted to foster debate, information sharing, and lively discussion. Free drinks during early networking, followed by seminar and dinner at a nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Monitoring the Situation: Bitcoin News Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>A casual BitPlebs meetup at Manuel's Tavern to discuss current news in Bitcoin, Privacy and Freedom Tech—including CLARITY ACT, KOSA, BIP 110, and more. Geared towards helping attendees learn about how to get bitcoin, use bitcoin, and understand where it fits into current events.</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Despite being an in-person event in Georgia, it has zero mention of AI, machine learning, or automation, triggering the automatic 1 score per the primary criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #1</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>A casual 5th Wednesday meetup hosted by the Georgia Bitcoin Council for the Atlanta bitcoin community. Each event creates space to discuss political issues surrounding bitcoin and freedom-tech, with some gatherings featuring guest speakers and others focusing on community presentations and open discussion.</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #8</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>A meetup for people exploring Bitcoin from a product perspective, focusing on tools, apps, and services that make Bitcoin usable and valuable to real people. Features five 15-minute demo slots where presenters walk through something they've been working on, with live demos, short talks, Q&amp;A, and constructive feedback.</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>A fun BitPlebs meetup at ATL BitLab. Tonight's topic is TBD but will certainly involve bitcoin. Meetups help attendees learn the basics of bitcoin and socialize with other bitcoiners, with time for presentations, moderated discussion, general bitcoin Q&amp;A, and socializing.</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #53</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs every third Wednesday for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning. Events are formatted to foster debate, information sharing, and lively discussion. Free drinks during early networking, followed by seminar and dinner at a nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation—it is exclusively about Bitcoin and Lightning Network technology, which triggers the automatic 1 rating regardless of its excellent in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>A casual BitPlebs meetup at Manuel's Tavern geared towards helping attendees learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for free beverages. Includes kick-off announcements, a presentation, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>This event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #9</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>A meetup for people exploring Bitcoin from a product perspective, focusing on tools, apps, and services that make Bitcoin usable and valuable to real people. Features five 15-minute demo slots where presenters walk through something they've been working on, with live demos, short talks, Q&amp;A, and constructive feedback.</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of other positive factors like being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>A fun BitPlebs meetup at ATL BitLab. Tonight's topic is TBD but will certainly involve bitcoin. Meetups help attendees learn the basics of bitcoin and socialize with other bitcoiners, with time for presentations, moderated discussion, general bitcoin Q&amp;A, and socializing.</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Despite being an in-person event in Atlanta, it has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating per the primary criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #54</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs every third Wednesday for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning. Events are formatted to foster debate, information sharing, and lively discussion. Free drinks during early networking, followed by seminar and dinner at a nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria regardless of being an in-person event in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>A casual BitPlebs meetup at Manuel's Tavern geared towards helping attendees learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for free beverages. Includes kick-off announcements, a presentation, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #2</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>A casual 5th Wednesday meetup hosted by the Georgia Bitcoin Council for the Atlanta bitcoin community. Each event creates space to discuss political issues surrounding bitcoin and freedom-tech, with some gatherings featuring guest speakers and others focusing on community presentations and open discussion.</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #10</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>A meetup for people exploring Bitcoin from a product perspective, focusing on tools, apps, and services that make Bitcoin usable and valuable to real people. Features five 15-minute demo slots where presenters walk through something they've been working on, with live demos, short talks, Q&amp;A, and constructive feedback.</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which triggers an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #55 - pre-TABConf</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning, held as a pre-TABConf event. Formatted to foster debate, information sharing, and lively discussion. Free drinks during early networking, followed by seminar and dinner at a nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of being an in-person event in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>A fun BitPlebs meetup at ATL BitLab. Tonight's topic is TBD but will certainly involve bitcoin. Meetups help attendees learn the basics of bitcoin and socialize with other bitcoiners, with time for presentations, moderated discussion, general bitcoin Q&amp;A, and socializing.</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, triggering an automatic score of 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>A casual BitPlebs meetup at Manuel's Tavern geared towards helping attendees learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for free beverages. Includes kick-off announcements, a presentation, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>July 2, 2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>6:00 PM EST</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>A casual BitPlebs meetup at Manuel's Tavern geared towards helping attendees learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for free beverages. Includes kick-off announcements, a presentation, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of location or format.</t>
         </is>
       </c>
     </row>

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Rejected Events" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Already on Calendar" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -134,9 +133,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K7" headerRowCount="1">
-  <autoFilter ref="A1:K7"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:L6" headerRowCount="1">
+  <autoFilter ref="A1:L6"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
     <tableColumn id="3" name="Confidence"/>
@@ -145,18 +144,19 @@
     <tableColumn id="6" name="URL"/>
     <tableColumn id="7" name="Start Time"/>
     <tableColumn id="8" name="Location"/>
-    <tableColumn id="9" name="Status"/>
-    <tableColumn id="10" name="Description"/>
-    <tableColumn id="11" name="Fit Reason"/>
+    <tableColumn id="9" name="Signup Link"/>
+    <tableColumn id="10" name="Status"/>
+    <tableColumn id="11" name="Description"/>
+    <tableColumn id="12" name="Fit Reason"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K6" headerRowCount="1">
-  <autoFilter ref="A1:K6"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:L10" headerRowCount="1">
+  <autoFilter ref="A1:L10"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
     <tableColumn id="3" name="Confidence"/>
@@ -165,9 +165,10 @@
     <tableColumn id="6" name="URL"/>
     <tableColumn id="7" name="Start Time"/>
     <tableColumn id="8" name="Location"/>
-    <tableColumn id="9" name="Status"/>
-    <tableColumn id="10" name="Description"/>
-    <tableColumn id="11" name="Fit Reason"/>
+    <tableColumn id="9" name="Signup Link"/>
+    <tableColumn id="10" name="Status"/>
+    <tableColumn id="11" name="Description"/>
+    <tableColumn id="12" name="Fit Reason"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
 </table>
@@ -462,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -472,10 +473,11 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,15 +523,20 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Signup Link</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fit Reason</t>
         </is>
@@ -538,294 +545,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>From prototype to production with Kiro &amp; Kiro CLI</t>
+          <t>SCL Course: Machine Learning Applications for Supply Chain Planning (Virtual/Instructor-Lead)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46212</v>
+        <v>46279</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6:00 PM EDT</t>
+          <t>1:00 PM EDT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Virtual/Instructor-led</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>https://ai.gatech.edu/event/scl-course-machine-learning-applications-supply-chain-planning-virtualinstructor-lead</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>The event title and description contain no mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of Georgia focus or other factors.</t>
+          <t>Apply machine learning with Python and Power BI to optimize supply chain forecasting, inventory, and maintenance.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with clear machine learning content hosted by Georgia Tech (a Georgia institution), which qualifies it for a mid-to-high score despite not being in-person.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Using Generative AI on Structured Data</t>
+          <t>SCL Course: Generative AI Application for Supply Chain Professionals (Virtual/Instructor-led)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46209</v>
+        <v>46496</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6:30 PM EDT</t>
+          <t>8:00 PM EDT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Virtual/Instructor-led</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>https://ai.gatech.edu/event/scl-course-generative-ai-application-supply-chain-professionals-virtualinstructor-led-0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear AI content (generative AI on structured data) but no Georgia focus or host organization information provided, and minimal event details available.</t>
+          <t>Participants will explore generative AI fundamentals, prompt engineering, and practical applications such as automated inventory systems, predictive maintenance, and route optimization.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with strong AI content (generative AI, prompt engineering, applications) hosted by Georgia Tech institution scores highly despite not being in-person.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>How to Use AI for Academic Research</t>
+          <t>SCL Course: Generative AI Application for Supply Chain Professionals (Onsite/In-Person)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46214</v>
+        <v>46678</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9:00 AM EDT</t>
+          <t>8:00 PM EDT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Georgia Tech Savannah</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>https://ai.gatech.edu/event/scl-course-generative-ai-application-supply-chain-professionals-onsitein-person</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear AI content (academic research applications) but no Georgia focus or hosting institution mentioned, and minimal event details provided.</t>
+          <t>Participants will explore generative AI fundamentals, prompt engineering, and practical applications such as automated inventory systems, predictive maintenance, and route optimization.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>In-person Georgia Tech event with substantial AI content (generative AI fundamentals, prompt engineering, supply chain applications) that is educational rather than a sales pitch.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS: Build Resilient Multi-Step Applications With Just Code</t>
+          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Pla...</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46219</v>
+        <v>46239</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
+          <t>11:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/tech-educational-panel</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Virtual AWS technical event with AI/automation relevance (multi-step applications, resilient systems) hosted for Georgia audience, though short description limits confidence in AI content depth.</t>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>The event description is empty with no mention of AI, machine learning, or automation in the title or available details, making it an automatic 1 despite the Georgia-based organization.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FREE REMOTE | LADIES IN AI - We Learn. We Share. We Laugh.</t>
+          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46219</v>
+        <v>46252</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>7:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Event has clear AI focus ('Ladies in AI') and is free/educational, but lacks location specificity, Georgia connection, and detailed description to assess whether it's a Georgia-focused or Georgia-hosted virtual event versus a generic national event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GA AI Alliance Networking Lunch</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>July 5, 2026</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>11:45 AM EDT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>In-person Georgia event with AI-relevant organization (GA AI Alliance) but minimal description prevents higher rating; networking lunch format suggests social rather than educational content.</t>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>AIMST is a known AI conference (strong fit for AI content), marked as in-person which scores highest, and hosted/promoted by Georgia Manufacturing Alliance suggesting Georgia relevance, though missing specific location details and event description reduce confidence slightly.</t>
         </is>
       </c>
     </row>
@@ -843,20 +826,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,15 +886,20 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Signup Link</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fit Reason</t>
         </is>
@@ -919,7 +908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Find a Startup to Help or Join</t>
+          <t>Coffee and Connections - Atlanta 7-16-2026</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -935,40 +924,45 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6:00 PM EDT</t>
+          <t>8:30 AM EDT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/coffee-and-connections---atlanta-7-16-2026</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Atlanta Tech Meet-Up</t>
+          <t>Networking Luncheon - Atlanta 7-16-2026</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -980,44 +974,49 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46210</v>
+        <v>46219</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6:00 PM EDT</t>
+          <t>11:30 AM EDT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/networking-luncheon---atlanta-7-16-2026</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python Atlanta Meetup (In Person!)</t>
+          <t>WGMA Paint the Town- The Davis Companies</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1029,44 +1028,45 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
+          <t>11:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/wgma-paint-the-town--the-davis-companies</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or available description, triggering an automatic score of 1 regardless of other factors.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open House!</t>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1078,44 +1078,49 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46217</v>
+        <v>46233</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7:30 PM EDT</t>
+          <t>9:00 AM EDT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Gainesville</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering automatic score of 1 per criteria.</t>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bytes &amp; Bites @ Krog St Market</t>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville - AFTERNOON</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1127,37 +1132,250 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>July 5, 2026</t>
+          <t>July 9, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11:45 AM EDT</t>
+          <t>11:30 AM EDT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Krog St Market</t>
+          <t>Gainesville</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville---afternoon</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Women of GMA Virtual Networking Event 8/11/26</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>July 9, 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/women-of-gma-virtual-networking-event-81126</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coffee and Connections - Atlanta 8-20-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>July 9, 2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/coffee-and-connections-atlanta-8-20-2026</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Networking Luncheon - Atlanta 8-20-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>July 9, 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/networking-luncheon-atlanta-8-20-2026</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026 Georgia Manufacturing Summit</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>July 9, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/2026-georgia-manufacturing-summit</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>The event title and available description contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or in-person status.</t>
         </is>
       </c>
     </row>
@@ -1167,88 +1385,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Event Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Fit Score</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Date Scraped</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Start Time</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fit Reason</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -472,7 +472,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Virtual-only event with clear machine learning content hosted by Georgia Tech (a Georgia institution), which qualifies it for a mid-to-high score despite not being in-person.</t>
+          <t>Virtual event with clear ML/AI content hosted by Georgia Tech (a Georgia institution), scoring above the typical virtual event baseline, but not reaching higher tiers since it's not in-person and appears to be a paid training course rather than a broader educational discussion.</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Virtual event with strong AI content (generative AI, prompt engineering, applications) hosted by Georgia Tech institution scores highly despite not being in-person.</t>
+          <t>Virtual event hosted by Georgia Tech (a Georgia institution) with strong AI content covering generative AI fundamentals and practical supply chain applications, scoring 3-4 per Georgia Tech virtual event criteria, elevated to 4 for substantive technical focus.</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>In-person Georgia Tech event with substantial AI content (generative AI fundamentals, prompt engineering, supply chain applications) that is educational rather than a sales pitch.</t>
+          <t>In-person Georgia Tech event with strong AI content (generative AI, prompt engineering, practical applications), though it appears to be a paid training course rather than a purely educational conference.</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11:00 AM EDT</t>
+          <t>11:00 AM - 1:30 PM EDT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -762,7 +762,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>The event description is empty with no mention of AI, machine learning, or automation in the title or available details, making it an automatic 1 despite the Georgia-based organization.</t>
+          <t>The event description is empty with no mention of AI, machine learning, or automation in the title or available details, making it an automatic 1 per criteria despite the Georgia-based organization.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AIMST is a known AI conference (strong fit for AI content), marked as in-person which scores highest, and hosted/promoted by Georgia Manufacturing Alliance suggesting Georgia relevance, though missing specific location details and event description reduce confidence slightly.</t>
+          <t>AIMST is a known AI conference with in-person format, Georgia connection through GMA signup link, and clear AI focus, but minimal description details reduce confidence slightly.</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8:30 AM EDT</t>
+          <t>8:30 AM - 10:00 AM EDT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -955,7 +955,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of in-person Atlanta location.</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11:30 AM EDT</t>
+          <t>11:30 AM - 1:00 PM EDT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1009,7 +1009,7 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11:00 AM EDT</t>
+          <t>11:00 AM - 1:00 PM EDT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or available description, triggering an automatic score of 1 regardless of other factors.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering an automatic 1 score regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9:00 AM EDT</t>
+          <t>9:00 AM - 12:00 PM EDT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1113,7 +1113,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11:30 AM EDT</t>
+          <t>11:30 AM - 4:00 PM EDT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+          <t>The event is a factory tour with zero mention of AI, machine learning, or automation in the title or description, making it an automatic 1 regardless of location.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3:30 PM EDT</t>
+          <t>3:30 PM - 4:30 PM EDT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8:30 AM EDT</t>
+          <t>8:30 AM - 10:00 AM EDT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1271,7 +1271,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person format.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11:30 AM EDT</t>
+          <t>11:30 AM - 1:00 PM EDT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1325,7 +1325,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+          <t>The event is a generic networking luncheon with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7:00 AM EDT</t>
+          <t>7:00 AM - 4:00 PM EDT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>The event title and available description contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or in-person status.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other criteria.</t>
         </is>
       </c>
     </row>

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -133,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:L6" headerRowCount="1">
-  <autoFilter ref="A1:L6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:L7" headerRowCount="1">
+  <autoFilter ref="A1:L7"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -154,8 +154,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:L10" headerRowCount="1">
-  <autoFilter ref="A1:L10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:L9" headerRowCount="1">
+  <autoFilter ref="A1:L9"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Virtual event with clear ML/AI content hosted by Georgia Tech (a Georgia institution), scoring above the typical virtual event baseline, but not reaching higher tiers since it's not in-person and appears to be a paid training course rather than a broader educational discussion.</t>
+          <t>Virtual event with strong AI/ML content (machine learning applications) hosted by Georgia Tech, a Georgia institution, which elevates it above the typical virtual-only score.</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Virtual event hosted by Georgia Tech (a Georgia institution) with strong AI content covering generative AI fundamentals and practical supply chain applications, scoring 3-4 per Georgia Tech virtual event criteria, elevated to 4 for substantive technical focus.</t>
+          <t>Virtual event hosted by Georgia Tech with substantive AI content (generative AI fundamentals, prompt engineering, practical supply chain applications), meeting the criteria for Georgia institution-hosted virtual events scoring 3-4.</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>In-person Georgia Tech event with strong AI content (generative AI, prompt engineering, practical applications), though it appears to be a paid training course rather than a purely educational conference.</t>
+          <t>In-person Georgia Tech event with substantive AI content (generative AI, prompt engineering, supply chain applications) that appears educational rather than a sales pitch.</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>The event description is empty with no mention of AI, machine learning, or automation in the title or available details, making it an automatic 1 per criteria despite the Georgia-based organization.</t>
+          <t>The event title and description contain zero explicit mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,57 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AIMST is a known AI conference with in-person format, Georgia connection through GMA signup link, and clear AI focus, but minimal description details reduce confidence slightly.</t>
+          <t>AIMST is a known AI conference with in-person format, hosted by Georgia Manufacturing Alliance (Georgia-focused organization), and explicitly mentions AI in the title, though the missing location field and empty description reduce confidence slightly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026 Georgia Manufacturing Summit</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>July 9, 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7:00 AM - 4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/2026-georgia-manufacturing-summit</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or available description, making it an automatic 1 regardless of location.</t>
         </is>
       </c>
     </row>
@@ -826,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -955,7 +1005,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of in-person Atlanta location.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1059,7 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+          <t>Event is a generic networking luncheon with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1109,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering an automatic 1 score regardless of other criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of other factors.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1163,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person status.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1217,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>The event is a factory tour with zero mention of AI, machine learning, or automation in the title or description, making it an automatic 1 regardless of location.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1267,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1321,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
         </is>
       </c>
     </row>
@@ -1325,57 +1375,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The event is a generic networking luncheon with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026 Georgia Manufacturing Summit</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>July 9, 2026</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>7:00 AM - 4:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/2026-georgia-manufacturing-summit</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other criteria.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of being in-person in Atlanta.</t>
         </is>
       </c>
     </row>

--- a/events_output_test.xlsx
+++ b/events_output_test.xlsx
@@ -133,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:L7" headerRowCount="1">
-  <autoFilter ref="A1:L7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:L79" headerRowCount="1">
+  <autoFilter ref="A1:L79"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -154,8 +154,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:L9" headerRowCount="1">
-  <autoFilter ref="A1:L9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:L113" headerRowCount="1">
+  <autoFilter ref="A1:L113"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Event Title"/>
     <tableColumn id="2" name="Fit Score"/>
@@ -463,17 +463,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1:00 PM EDT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Virtual/Instructor-led</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>https://ai.gatech.edu/event/scl-course-machine-learning-applications-supply-chain-planning-virtualinstructor-lead</t>
@@ -596,7 +592,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Virtual event with strong AI/ML content (machine learning applications) hosted by Georgia Tech, a Georgia institution, which elevates it above the typical virtual-only score.</t>
+          <t>Virtual event with clear ML content (machine learning with Python and Power BI) hosted by Georgia Tech, a Georgia institution, which qualifies it for a higher score despite being virtual-only.</t>
         </is>
       </c>
     </row>
@@ -619,7 +615,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -632,11 +628,7 @@
           <t>8:00 PM EDT</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Virtual/Instructor-led</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>https://ai.gatech.edu/event/scl-course-generative-ai-application-supply-chain-professionals-virtualinstructor-led-0</t>
@@ -654,7 +646,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Virtual event hosted by Georgia Tech with substantive AI content (generative AI fundamentals, prompt engineering, practical supply chain applications), meeting the criteria for Georgia institution-hosted virtual events scoring 3-4.</t>
+          <t>Virtual event with strong AI content (generative AI, prompt engineering, practical applications) hosted by Georgia Tech, a Georgia institution, which elevates it despite being virtual-only.</t>
         </is>
       </c>
     </row>
@@ -677,7 +669,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -712,7 +704,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>In-person Georgia Tech event with substantive AI content (generative AI, prompt engineering, supply chain applications) that appears educational rather than a sales pitch.</t>
+          <t>In-person Georgia Tech event with substantial AI content (generative AI fundamentals, prompt engineering, practical supply chain applications), though it appears to be paid training rather than an open educational talk.</t>
         </is>
       </c>
     </row>
@@ -735,7 +727,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -745,7 +737,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11:00 AM - 1:30 PM EDT</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -762,7 +754,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>The event title and description contain zero explicit mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+          <t>Event details lack any mention of AI, machine learning, or automation in the title or short description, making it an automatic 1 despite being Georgia-focused.</t>
         </is>
       </c>
     </row>
@@ -785,7 +777,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -808,57 +800,3825 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AIMST is a known AI conference with in-person format, hosted by Georgia Manufacturing Alliance (Georgia-focused organization), and explicitly mentions AI in the title, though the missing location field and empty description reduce confidence slightly.</t>
+          <t>AIMST is a known AI-focused conference and this is an in-person event with Georgia involvement (GMA - Georgia Manufacturing Alliance), but the minimal event description and missing location details prevent a higher confidence score.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026 Georgia Manufacturing Summit</t>
+          <t>AIMST 2026 - AI Manufacturing &amp; SCADA Technology Conference and Exhibition</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.meetmax.com/sched/event_130973/investor_reg_new.html?attendee_role_id=TWST2_ATTENDEE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3 days of cutting-edge content on smart manufacturing, IT/OT, digital transformation, cybersecurity, and AI &amp; IIoT with 60+ speakers, 350+ attendees, and 8+ networking events</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference in Atlanta with explicit focus on AI, manufacturing, digital transformation, and IIoT across 3 days with 60+ speakers and 350+ attendees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PAi Manufacturing Facility Tour</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Guided behind-the-scenes tour of a 120,000 sq. ft. production facility featuring 50 CNC machining centers and 32 industrial robots. Complimentary for AIMST attendees. Advance registration required. Space is limited.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person Georgia event featuring industrial robots and automation technology, it lacks explicit mention of AI or machine learning in its description and appears to be primarily a facility tour rather than an educational AI event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Bias &amp; Governance: Building Trust in the Age of Enterprise AI presented by TAG Diversity, Equity &amp; Inclusion Society and TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/8EFKQ38sOCRC7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Join TAG DEI &amp; TAG DS&amp;AI for an executive forum on AI bias and governance, exploring how organizations can build enterprise AI that is both innovative and trustworthy</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with strong AI content (bias &amp; governance) hosted by TAG, a Georgia-focused organization, scoring at the upper end for Georgia-based virtual events despite missing explicit location confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>The TAG Fintech Innovation Challenge: Where Are They Now? presented by TAG Fintech Society</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/mwFE8ZYhmC3Ce</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a captivating panel discussion as three fintech founders share experiences growing their companies from the ground up.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with no explicit AI/machine learning content in the title or description (fintech founders panel), though hosted by Georgia-based TAG organization which slightly elevates it above a typical national webinar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cyber Resilience in the AI Era presented by TAG Cybersecurity &amp; Risk Management Society and TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/MwFNl0es8CeCg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content (Data Science &amp; AI Society co-host) and Georgia focus (TAG is Atlanta-based), but confidence is medium due to missing location confirmation and empty description field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rural AI Workforce Forum 2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/rural-ai-workforce-forum-2026-1759715?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Preparing rural communities for an AI-driven future.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI content focused on workforce development, hosted by TAG (Georgia-based organization), marked as in-person, but lacks specific location confirmation and has limited descriptive detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>From Forecasting to Demand Orchestration: How AI Is Redefining Supply Chain Planning presented by TAG Data Science &amp; AI Society and TAG Supply Chain, Logistics &amp; Manufacturing Society</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/WqFgM07iaCJCE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>You'll hear what's working now, what's still hard, and how companies across utilities, healthcare, financial services, retail, and CPG are using AI to move faster and smarter.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content (demand orchestration, AI in supply chain) hosted by TAG (Georgia-based organization), scoring above generic webinars but below in-person events due to virtual-only format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fintech South 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/12F2XblUgCVCB</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Superpowers for Good: Solving Society's Biggest Challenges presented by TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/xRF50ZqHMCYC7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>An inspiring evening showcasing complete, real-world data science and AI projects from concept to impact.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Educational AI event with clear AI/data science focus hosted by TAG (Georgia-based organization), scoring high despite being virtual because it's Georgia-focused and from a Georgia institution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IBM Certificate (in-Person) Graduation</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/EqFedRnCgC6C9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a special virtual celebration honoring the achievements of participants in the IBM SkillsBuild Program. This event recognizes learners from our recent cohorts who have dedicated their time and effort to building in-demand</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Event mentions IBM SkillsBuild Program and in-person format, suggesting AI/tech training relevance, but the description is incomplete and contradicts itself (says 'virtual celebration' despite in_person flag), making it unclear if the event itself focuses on AI content or is primarily a graduation ceremony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TAG-Ed 2026 Pathways to Leadership Summit &amp; Graduation</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>July 9, 2026</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>7:00 AM - 4:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/2026-georgia-manufacturing-summit</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or available description, making it an automatic 1 regardless of location.</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/OOFNE8dhaCqCD</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>TAG (Technology Association of Georgia) is a Georgia-focused organization and the event appears to be in-person, but the completely blank description and title lacking explicit AI/ML/automation mentions make it impossible to confirm the event content is AI-related rather than generic leadership training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Beyond Connected: IoT's Next Chapter presented by TAG Cloud Society</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>An executive panel exploring how leading organizations are transforming connected devices into intelligent, business-driven ecosystems.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event hosted by TAG (Georgia-focused org) with AI/automation relevance through intelligent IoT ecosystems, but lacks specific technical depth details and location ambiguity prevents higher scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>//Shift AI 2026</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/R1Fo7y2FRC0CX</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Join us for our kickoff AI Summit Event!</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>The event has clear AI content (AI Summit) and is in-person, but the missing location details and vague description prevent a higher score, though the TAG membership link suggests a Georgia-focused organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Annual DataPalooza presented by TAG Data Governance Society</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/kgFYW1VuzCVC1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>DataPalooza returns in 2026, bringing together Atlanta's data governance, privacy, and data management leaders for an evening of meaningful connection.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event hosted by Georgia-based TAG organization with data governance focus, but lacks explicit AI/ML/automation mention in title or description, preventing a higher score despite the Georgia connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026 TAG Invest Connect: Meet, Pitch, &amp; Partner</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/QZFMBR6tdCnC0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>TAG INVEST CONNECT is an annual event that connects Black tech entrepreneurs with the opportunity to pitch to investors looking for innovative</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>The event description mentions pitching and partnering with investors but contains zero explicit mention of AI, machine learning, or automation, making it an automatic 1 per the first criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026 Georgia Day of Code</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46360</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/oXFq4V1T6C2CB</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2026 Georgia Day of Code is a free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event hosted by TAG (Georgia-focused org) with educational coding content, but lacks explicit AI/ML/automation mention in the title or description, placing it at the lower end of the Georgia institution virtual event range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cumming AI + Coffee (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>7:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Cumming, GA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>In-person Georgia event with AI in the title hosted by an AI-focused organization (The AI Collective), but completely empty short description makes it impossible to assess the actual AI content and educational value of the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI HR Forum #01 w/ The AI Collective KC</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>The event title mentions AI but provides no description of actual AI content, appears to be a virtual-only forum with no Georgia connection, and lacks sufficient detail to confirm it's educational rather than a networking or sales event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Fundamentals for Qualitative Researchers (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>In-person educational AI event in Georgia (Alpharetta) with clear AI content focus, though the short description is empty which creates some uncertainty about depth and quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Make Your Story Stick (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Event title and description contain zero mention of AI, machine learning, or automation despite being hosted by an AI-focused organization, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>The Copilot Effect: Microsoft Fabric Copilot (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Event has no description provided to evaluate AI/ML content, and while the title mentions Microsoft Fabric Copilot (suggesting AI focus), it's a virtual-only event from a national corporate entity with insufficient details to confirm substantial educational value rather than a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Match Marketer Mixer w/ The AI Collective Atlanta</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description despite being associated with 'The AI Collective Atlanta' organization, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lunch &amp; Hack Online Series - What is Harness Engineering? (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>While the event title mentions 'Harness Engineering' which could relate to AI/ML systems, there is no explicit mention of AI, machine learning, or automation in the available description, and it is virtual-only without clear Georgia focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PNP - BUSINESS MATCHING OMNICHANNEL GT-MT-ECOM 2026 X AI AGENT</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>While the title mentions 'AI Agent,' the short description is empty and provides no evidence of actual AI content focus; combined with the minimal details, this appears to be a generic business matching event that may only tangentially reference AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>West Midtown AI Meetup (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI in title suggesting legitimate AI content, but minimal description and no signup link create uncertainty about actual substance and focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Demo Series: July Edition - Startup Grind + AI Collective + BFC</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>7:30 PM PDT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Event has AI content in title and involves demo/discussion format, but is virtual-only with no clear Georgia focus, missing location/description details, and no indication it's hosted by a Georgia institution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI in Flooring (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>11:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Dalton, GA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with AI in the title, but extremely sparse details (no description, unclear format/content) make it difficult to assess whether it's a substantive educational/industry discussion or a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Macon Chapter Kickoff (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Macon, GA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with AI-related organization (The AI Collective) but extremely limited description prevents full assessment of actual AI content and educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>The Copilot Effect: Power Platform Copilot (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Event has no description content to evaluate AI/ML relevance, and while the title mentions 'Copilot' (suggesting AI content), the virtual-only format with no Georgia focus and missing details prevent confident scoring above the baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Building with AI: Hartford-Micro Hackathon (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Event clearly involves AI (hackathon with AI focus), but virtual-only format with no Georgia connection and missing critical details (location blank, no description, no signup link) limit confidence and fit assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Technology, AI and Addictive Behaviors: Can They Be Treated?</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with clear AI content in title, but no indication of Georgia focus or hosting institution, and the short description is blank making it difficult to assess whether this is educational or promotional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Assessment Workshop: Partnering with AI Before the School Year Begins</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Atlanta · Mount Vernon School, Upper Campus</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-assessment-workshop-partnering-with-ai-before-the-school-year-begins-tickets-1992480807732?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI focus (AI assessment and partnering with AI), though the empty description and educational/workshop nature (potentially training-heavy) prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Marietta, GA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/strategic-prompt-design-for-ai-1-day-training-in-marietta-ga-tickets-1992104255454?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Georgia with clear AI content (prompt design), it appears to be a paid training focused on a specific skill rather than educational discussion, and the empty description limits assessment of its depth and value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Builders #20: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044232/</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>First Wednesday monthly lunch event covering latest AI tools, LLM integration, generative AI, and text-to-image/video. Bring your own lunch or door dash something to the Lab.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI content focus (LLM integration, generative AI, text-to-image/video) hosted by a local lab, scoring highest for Georgia location while being an educational discussion format rather than a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The AI Underground - Conference</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://aiunderground.dev</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Conference for people building the future of freedom with AI, featuring open weight models and open source agents.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference in Atlanta with clear focus on AI technology (open weight models, open source agents), strong location match, and substantive educational content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Builders #21: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044241/</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Monthly lunch event covering latest AI tools, LLM integration, generative AI and models. All skill levels welcome.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta, Georgia with clear AI/LLM content focus, educational format suited for all skill levels, hosted by a local meetup group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Builders #22: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044251/</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Monthly lunch event covering latest AI tools, LLM integration, generative AI and models. All skill levels welcome.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with strong AI content focus (LLM integration, generative AI, models) hosted by a local meetup organization, scoring highest for in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Building a Mini-Software Factory using Pi.dev and Local LLMs</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-ship-and-social/events/315614874/?recId=07478199-cd17-44a9-b2f3-8b457041a5a2&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with clear AI/LLM technical content (Pi.dev and Local LLMs), though confidence is medium due to missing detailed description and inability to verify exact city within Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GA AI Alliance Networking Lunch</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>11:45 AM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/315317984/?recId=07478199-cd17-44a9-b2f3-8b457041a5a2&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Georgia (positive factors) but has no description provided, making it impossible to verify AI/ML content or assess whether it's a substantive AI event versus a generic networking mixer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Build an Agent Day - Atlanta</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/all-things-ai-live/events/315468219/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with clear AI focus ('Build an Agent Day') that appears to be an educational/technical event, though the empty short_description and lack of detailed content creates some uncertainty about the full scope and whether it might be sales-oriented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/312398713/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Monthly Meetup + Game Night: July 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atl-ai/events/314482298/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or short description, making it an automatic 1 despite being in-person in Georgia and hosted by what appears to be an AI-focused meetup group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Meet Atlanta Tech Week &amp; RenderATL Speakers! (REGISTER ON LUMA)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/react-atl/events/315658340/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>The event description is empty and the title makes no mention of AI, machine learning, or automation, so it fails the automatic criterion regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI Skills Course with Kilo Code</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-society-for-business-intelligence/events/315696138/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Event is in Georgia and in-person (positive factors), but the short description is empty, making it impossible to verify AI/ML content, and 'AI Skills Course' with a training vendor suggests paid training/sales pitch rather than educational discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI-Driven Engineering Workshop: Building Smarter Teams, Faster Workflows</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/modernwebatl/events/315289936/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content in title but is virtual-only with missing location details and empty description, and while hosted by Modern Web ATL (Atlanta-based), insufficient detail about Georgia focus or content substance prevents higher scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/315410843/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FREE REMOTE | LADIES IN AI - We Learn. We Share. We Laugh.</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-growth-circle/events/315016393/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Event title mentions 'Ladies in AI' with clear AI focus, but the virtual-only format with blank location and empty description makes it difficult to confirm Georgia relevance or assess the event's substantive content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>The AI Underground - Conference</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315123423/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference in Georgia with a clear AI focus in the title, though the empty short description and lack of detailed content information prevents a higher confidence rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Atlanta DUG Meeting - August</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/microsoft-dynamics-meetup-of-atlanta/events/315486549/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description - it appears to be a Microsoft Dynamics user group meeting with no AI content indicated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AIDataTech Connect: Global Virtual Networking Event for AI, Data &amp; Tech Pros</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ac-atl/events/313188283/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI/data/tech focus passes the AI content requirement, but lacks location confirmation and has an empty description, and while the signup link suggests an Atlanta meetup group (AC-ATL), this cannot be definitively confirmed from the provided event details alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Python Atlanta Meetup (In Person!)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>7:30 PM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/python-atlanta/events/314101563/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, which is an automatic 1 per the criteria, despite being an in-person event in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>The Power of Google NotebookLM &amp; Gemini</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-ai-builders/events/315342676/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content (Google NotebookLM &amp; Gemini) hosted by Atlanta AI Builders, a Georgia-focused organization, but lacks full event details and location confirmation that would enable a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Welcome to CoLabGA: Coffee, Code, Collaborate!</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/columbusgadatascience/events/315560804/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain no mention of AI, machine learning, or automation, making it an automatic 1 per the primary criterion despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Monthly 2600 Meeting!</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ethical-hackers/events/315395630/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>The event title and short description contain zero mention of AI, machine learning, or automation, making it an automatic 1 despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Atlanta dbt Lowkey Meetup [In Person] : Data, Drinks &amp; Community</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-dbt-meetup-group/events/315472808/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Georgia (positive factors) but has zero mention of AI, machine learning, or automation in title/description, making it an automatic 1 per criteria, though the in-person Georgia location and dbt's data engineering relevance provide some mitigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ship It Sundays: August 2026</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atl-ai/events/314494639/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DC470 Meetup</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ethical-hackers/events/315395667/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Civic Action Night at Tech Square ATL (TSQATL) Social Club</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Tech Square ATL, Georgia</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/civictechatlanta/events/313899226/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TechConnect: Global Virtual Job &amp; Networking Event for Data, AI, and Tech Pros</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ac-atl/events/313188287/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI/data focus but no Georgia-specific mention, hosted via Meetup with minimal description details to assess educational value versus networking/sales intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Rust-Atl</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/rust-atl/events/313539329/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI Builders #20: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044232/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with clear AI focus in title (AI Builders), though the empty short description limits confidence about specific content quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Atlanta Computer Club DOT Com Monthly Meetup</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-computer-club-dot-com/events/314736588/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Open Build Night</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/geekspace-gwinnett/events/315522761/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DBAtlanta - staying alive?</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/dbatlanta/events/315686736/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation - it appears to be a database administrator meetup with no AI content despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Weekly Open House</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/sandbox-atlanta/events/315446769/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Secure AI Hackathon | 24 Hr Online | Register Link ⬇️</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/microsoft-fabric-tour-atlanta-seattle-data-ai-security/events/315580836/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content (Secure AI Hackathon) but is virtual-only with no Georgia focus mentioned, and the extremely sparse description limits ability to assess educational value versus sales intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FREE REMOTE | LADIES IN AI - We Learn. We Share. We Laugh.</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-growth-circle/events/315016411/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI focus (Ladies in AI) and is free, but lacks sufficient detail about content, Georgia connection, or organizer to score higher, and the virtual-only format with missing location and empty description limits confidence despite the promising title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GAIL executive coding Jam session 1</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/google-developer-groups-gdg-atlanta/events/315294141/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>The event has no description available and the title 'GAIL executive coding Jam session 1' does not explicitly mention AI, machine learning, or automation, making it impossible to confirm AI content as required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Building an AI resume optimization tool with Matthew Christiansen: Session 2</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/google-developer-groups-gdg-atlanta/events/315294142/?recId=261b62a2-b8c8-4719-93bf-7d39603f99e3&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event hosted by GDG Atlanta (Georgia-focused organization) with clear AI content (building an AI resume optimization tool), but lacks detailed description and location confirmation that would elevate the score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Escape the 9–5 Live | NO B.S. AI with Bobby</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/joingps/events/315531063/?recId=261b62a2-b8c8-4719-93bf-7d39603f99e3&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Event has no description provided and title 'NO B.S. AI with Bobby' mentions AI but is too vague to confirm substantive AI content versus a generic motivational talk, combined with missing location data and no other details to assess the event's actual focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Q&amp;AI Weekly — Build Real AI Skills (Live with Bobby V.)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/joingps/events/315531455/?recId=261b62a2-b8c8-4719-93bf-7d39603f99e3&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Event clearly mentions AI in title and appears to be an educational/skills-building session, but it is virtual-only with no Georgia focus indicated, no organization details provided, and crucially lacks a description that would confirm the AI content depth or location/organizer context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fueling the Future: The Strategic Role of Synthetic Data in AI Workflows</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/bigdataatl/events/314212539/?recId=261b62a2-b8c8-4719-93bf-7d39603f99e3&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with strong AI content (synthetic data in AI workflows) hosted by Big Data ATL, a Georgia-focused meetup organization, which elevates it above a typical national corporate webinar despite missing location confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Operationalizing Agentic AI</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/artificial-intelligence-atl/events/315068169/?recId=261b62a2-b8c8-4719-93bf-7d39603f99e3&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with strong AI content (agentic AI operationalization) hosted by Atlanta-based AI meetup group, but lacks description details and confirmed Georgia focus to score higher.</t>
         </is>
       </c>
     </row>
@@ -876,17 +4636,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
@@ -958,7 +4718,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Coffee and Connections - Atlanta 7-16-2026</t>
+          <t>WGMA Paint the Town- The Davis Companies</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -970,11 +4730,11 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -984,17 +4744,13 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8:30 AM - 10:00 AM EDT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/coffee-and-connections---atlanta-7-16-2026</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/wgma-paint-the-town--the-davis-companies</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1005,14 +4761,14 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Networking Luncheon - Atlanta 7-16-2026</t>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1024,11 +4780,11 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46219</v>
+        <v>46233</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1038,17 +4794,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11:30 AM - 1:00 PM EDT</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gainesville</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/networking-luncheon---atlanta-7-16-2026</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1059,14 +4815,14 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Event is a generic networking luncheon with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of being an in-person event in Georgia.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WGMA Paint the Town- The Davis Companies</t>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville - AFTERNOON</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1078,11 +4834,11 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1092,13 +4848,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11:00 AM - 1:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gainesville</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/wgma-paint-the-town--the-davis-companies</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville---afternoon</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1109,14 +4869,14 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of other factors.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville</t>
+          <t>Women of GMA Virtual Networking Event 8/11/26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1128,11 +4888,11 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1142,17 +4902,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9:00 AM - 12:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Gainesville</t>
-        </is>
-      </c>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/women-of-gma-virtual-networking-event-81126</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1163,14 +4919,14 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person status.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville - AFTERNOON</t>
+          <t>Coffee and Connections - Atlanta 8-20-2026</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1182,11 +4938,11 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46233</v>
+        <v>46254</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1196,17 +4952,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11:30 AM - 4:00 PM EDT</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Gainesville</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville---afternoon</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/coffee-and-connections-atlanta-8-20-2026</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1217,14 +4973,14 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Women of GMA Virtual Networking Event 8/11/26</t>
+          <t>Networking Luncheon - Atlanta 8-20-2026</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1236,11 +4992,11 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1250,13 +5006,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3:30 PM - 4:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/women-of-gma-virtual-networking-event-81126</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/networking-luncheon-atlanta-8-20-2026</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,14 +5027,14 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of location.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coffee and Connections - Atlanta 8-20-2026</t>
+          <t>Southeastern Hose - Bremen</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1286,11 +5046,11 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1300,17 +5060,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8:30 AM - 10:00 AM EDT</t>
+          <t>1:30 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/coffee-and-connections-atlanta-8-20-2026</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/southeastern-hose---bremen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1321,14 +5081,14 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Networking Luncheon - Atlanta 8-20-2026</t>
+          <t>2026 Georgia Manufacturing Summit</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1340,11 +5100,11 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46254</v>
+        <v>46280</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>July 9, 2026</t>
+          <t>July 16, 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1354,17 +5114,13 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11:30 AM - 1:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
+          <t>7:00 AM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/networking-luncheon-atlanta-8-20-2026</t>
+          <t>https://www.georgiamanufacturingalliance.com/events/2026-georgia-manufacturing-summit</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1375,7 +5131,5447 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of being in-person in Atlanta.</t>
+          <t>Event title and description contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Building Impact Together: A Tech Collaboration &amp; Volunteer Event</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/building-impact-together-a-tech-collaboration-volunteer-event-1759631?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>The event title and short description contain zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026 Summer Social presented by TAG Digital Health Society</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/4lF9eElfRCMCx</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Join TAG's Digital Health Society for an evening of connection and collaboration at our 2026 Summer Social!</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation - it is merely a social mixer, which triggers the automatic 1 score regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Israeli Cybersecurity Summit</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/b3FyYn6TNCRCw</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IBM SkillsBuild Orientation</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and demo on how to access the learning platform</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation—it is a generic program orientation covering structure, expectations, and platform access, triggering the automatic 1 rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/EqF6GN4IgC6C9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is purely a social happy hour—making it an automatic 1 regardless of it being hosted by TAG (a Georgia-focused AI organization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/VeFAOextNCeC9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>This 30-minute session is led by Lili Orozco from Member Services. This session will focus on the following topics: TAG's mission and objectives, how to activate your membership, how to maximize your benefits as a member. Sessions repeat monthly.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>This is a generic membership orientation with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of TAG being a Georgia-focused AI organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TAG-Ed Pathways to Leadership Virtual Open House</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Join us for an inside look at the Pathways to Leadership program, a year-long leadership experience designed for emerging and mid-level professionals. During this session, you'll learn about the program's structure and benefits and hear from graduates</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of being hosted by TAG (a Georgia-focused organization) or its virtual format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/7EFZQMQsNCQCd</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>This is a generic membership orientation with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/VeFXK8WSNCeC9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>The event description mentions zero AI, machine learning, or automation content - it is purely a social happy hour, which triggers the automatic 1 rating regardless of TAG being a Georgia-focused organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/nvF6MwdSECNCZ</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation—it is solely described as a happy hour networking event, which triggers the automatic 1 rating regardless of it being hosted by TAG (a Georgia-focused AI organization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/3BFg2ejHYCQCg</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>This is a generic membership orientation with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46328</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/jKFGO1mfZCkCE</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation—it is purely a social happy hour—which automatically results in a score of 1 regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46329</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/9eFlWx1fWC9Cx</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>The event is an introductory membership orientation with zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of being hosted by TAG (a Georgia-focused organization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[Pending] Veterans Day presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46331</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TAG Chairs' Gala 2026</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46345</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TAG 101- An Introduction to your TAG Membership</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/xRFXAz4IMCYC7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>This is a generic membership orientation with zero mention of AI, machine learning, or automation in the title or description, making it an automatic 1 regardless of TAG's status as a Georgia AI organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Members Only - TAG Converge Series - TAG Hour</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46363</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/G9FwqlWUNCxCK</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>This will be the ultimate happy hour experience where connections are made, and fun is had!</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation—it is purely a social happy hour networking event, which automatically scores 1 regardless of TAG's Georgia-focused AI mission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Miami)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Florida (FL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Build Practical Agents with Hermes (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Tennessee (TN), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Watch the FIFA World Cup Final in Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan, Malaysia</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Malaysia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Closing Session, AI x Mental Health Series | Breathwork, Sound Bath &amp; Yoga (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Location is in District of Columbia (DC), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI and the Future of Work (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Manassas, VA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Pioneer Day: A Pie &amp; Beer Mixer</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>6:00 PM MDT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>South Salt Lake, UT</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Utah (UT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI and the Future of Work (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Location is in North Carolina (NC), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Building with AI: Open Mic Night (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Founder Fridays: The AI Collective x Unstuck Labs</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>9:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AIC Masterclass Series: Build Your GTM Engine with Claude</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3:30 AM GMT+5:30</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Location is in India, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gemini Student Build — Portland (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1:00 PM PDT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Oregon (OR), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>El Futuro de la Inteligencia Artificial en Guatemala</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3:30 PM CST</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala, Guatemala</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Guatemala, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CT AI Community Talks (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Hartford, CT</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Demo Night: AWS x AI Collective</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Bouldering Social (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11:30 AM GMT+2</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>München, Germany</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Germany, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Builders Night: Demos, Feedback &amp; Collaboration</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>5:45 PM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Plano, TX</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C-Suite Dinner: The Full Arc of Operationalising AI (w/ FACCI &amp; The AI Collective) - FOLLOW LINK BELOW FOR TICKET</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3:00 AM GMT+9:30</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Adelaide, Australia</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Australia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ghana AI Awards 2026 (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Accra, Ghana</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ghana, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI Act, Day One: Building and Scaling Under Europe's New Rules — co-hosted by AWS</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>12:00 PM GMT+2</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Germany, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HeyGen is coming to Islamabad!!! | AI Avatar Pop-Up (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1:00 AM GMT+5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Islamabad, Pakistan</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Pakistan, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI &amp; Ayam: The Spice of Innovation</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>5:30 AM GMT+8</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Malaysia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI, liderazgo y talento</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Medellín, Colombia</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Colombia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Automatizaciones + IA: el futuro del trabajo manual (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2:30 PM GMT-3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Argentina, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Building AI You Can Stand Behind: Governance, Security, and Trust in Production (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>4:00 PM PDT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Least-Privilege AI Agents (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>9:30 PM PDT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Saratoga, CA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>No-Code Coding | Stamford AI Meetup | (w/ AI Collective)</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Space Coast AI Town Hall</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Cocoa, FL</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Florida (FL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SF DEMO NIGHT 🚀 (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>7:30 PM PDT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (San Francisco)</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8:00 PM PDT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Work in the GenAI Era: From AI Pilots to AI-Native Organizations (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Hartford, CT</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Chicago)</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Illinois (IL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Building with AI: Stamford Micro-Hackathon (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Step SF 2026: The AI &amp; Tech Startup Festival</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>11:00 AM PDT</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Austin)</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Portland)</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>8:00 PM PDT</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Oregon (OR), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Toronto)</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Canada, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>The AI Collective #2 Prague Meetup (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>11:00 AM GMT+2</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Hlavní město Praha, Czechia</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Czechia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AIC SF Chapter Team &amp; Volunteer Get-Together (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>8:00 PM PDT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is a team/volunteer social gathering, which triggers the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SUMMER BREAK - ENJOY AI-FREE TIME IN THE COTTAGE!</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>10:00 AM GMT+3</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Event title explicitly promotes avoiding AI and contains zero mention of AI, machine learning, or automation as educational or professional content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Parenting with AI (w/ The AI Collective Kansas City)</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Event title mentions AI but lacks any description of AI/ML content, appears to be a parenting advice session rather than an educational AI event, and is a virtual-only event not hosted by a Georgia institution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>🧠 The AI Collective Netherlands | September Meetup (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>11:00 AM GMT+2</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering automatic 1 rating per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Copy of AYIC Summer STEAM Camps</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Austell · Austell Youth Innovation Center</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/copy-of-ayic-summer-steam-camps-tickets-1990831929894?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026 Summer STEM Innovation Day</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Hinesville · Liberty County Performing Arts Center</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/2026-summer-stem-innovation-day-registration-1992705955154?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Next Play: Sports + Tech Experience for Kids &amp; Teens (Ages 6–17)</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Austell · Riverside EpiCenter</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/next-play-sports-tech-experience-for-kids-teens-ages-617-tickets-1988691259090?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STEM: 1- day Workshop for Students at Wandalands Vineyard &amp; Orchards</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Jackson · Wandalands Vineyard and Orchards, LLC</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/stem-1-day-workshop-for-students-at-wandalands-vineyard-orchards-tickets-1990070665933?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/modern-data-architecture-2-days-training-in-atlanta-ga-tickets-1992366361420?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Honeybee Hive Tour</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Columbus · 1830 Shepherd Dr</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/honeybee-hive-tour-tickets-1986742680840?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Stronger Communities Through Leadership Skills – 1 Day Training in Atlanta</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Atlanta · Regus - Atlanta - 260 Peachtree</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/stronger-communities-through-leadership-skills-1-day-training-in-atlanta-tickets-1702814948349?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of its Atlanta in-person location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AWS Solution Architect Training | 4-Day Bootcamp in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Atlanta · 260 Peachtree St suite 2200</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solution-architect-training-4-day-bootcamp-in-atlanta-ga-tickets-1987119022488?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person Atlanta event, it is a paid training bootcamp focused on AWS certification rather than AI/ML/automation content, and has zero mention of AI in its title or description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Monitoring the Situation: Bitcoin News Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044569/</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Bitcoin meetup discussing current news in Bitcoin, Privacy and Freedom Tech including CLARITY ACT, KOSA, BIP 110. Casual event with presentation and social discussion.</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a Bitcoin/cryptocurrency meetup focused on news and policy discussion, which triggers the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044682/</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Casual 5th Wednesday meetup for the Atlanta bitcoin community discussing political issues surrounding bitcoin and freedom-tech with guest speakers and open discussion.</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #8</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044356/</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Meetup for people exploring Bitcoin from a product perspective. Features five 15-minute demo slots with live demos, talks, Q&amp;A, and constructive feedback. Dinner at nearby restaurant follows.</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is focused on Bitcoin and blockchain technology, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044424/</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Bitcoin meetup featuring Bitcoin Season film screening and discussion about Bitcoin's infiltration of sports business and player empowerment.</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a Bitcoin meetup with film screening and sports business discussion, which triggers the automatic 1 rating regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #53</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044445/</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Third Wednesday monthly Socratic Seminar discussing latest Bitcoin and Lightning technological developments. Features debate, discussion topics, and dinner/hangout afterwards.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is exclusively about Bitcoin and Lightning Network technology, triggering the automatic 1 score regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044570/</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Casual BitPlebs meetup at Manuel's Tavern for learning basics of bitcoin and socializing with other bitcoiners. Free beverages and opportunity to order dinner.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is focused exclusively on Bitcoin education and socializing, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #9</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044357/</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Meetup for people exploring Bitcoin from a product perspective. Features five 15-minute demo slots with live demos, talks, Q&amp;A, and feedback. Dinner at nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is focused on Bitcoin from a product perspective, which triggers the automatic 1 rating regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044425/</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Bitcoin meetup with TBD topic. Casual event for learning basics and socializing with other bitcoiners, followed by dinner at nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is a Bitcoin/cryptocurrency meetup with no AI content, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #54</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044444/</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Third Wednesday monthly Socratic Seminar discussing latest Bitcoin and Lightning developments with debate, discussion topics, and dinner/hangout.</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is exclusively about Bitcoin and Lightning Network developments, which automatically scores it a 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044571/</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Casual BitPlebs meetup at Manuel's Tavern for learning about bitcoin and socializing. Free beverages and opportunity to order dinner.</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is solely about Bitcoin and socializing, which triggers the automatic 1 rating regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #2</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044686/</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Casual 5th Wednesday meetup discussing political issues surrounding bitcoin and freedom-tech with guest speakers and community presentations.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #10</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044359/</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Meetup for people exploring Bitcoin from a product perspective. Features five 15-minute demo slots with live demos, talks, Q&amp;A, and feedback. Dinner at nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is focused on Bitcoin and blockchain technology, which triggers the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #55 - pre-TABConf</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044442/</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Socratic Seminar discussing latest Bitcoin and Lightning developments with debate, discussion topics, and dinner/hangout.</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is exclusively about Bitcoin and Lightning Network developments, which triggers the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044426/</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Bitcoin meetup with TBD topic. Casual event for learning basics and socializing, followed by dinner at nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a Bitcoin/cryptocurrency meetup with no AI content, triggering the automatic 1 rating regardless of being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044572/</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Casual BitPlebs meetup at Manuel's Tavern for learning about bitcoin and socializing. Free beverages and opportunity to order dinner.</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is a bitcoin/cryptocurrency social meetup, which triggers the automatic 1 rating regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Ave NE, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044573/</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Casual BitPlebs meetup at Manuel's Tavern for learning about bitcoin and socializing. Free beverages and opportunity to order dinner.</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is focused on Bitcoin education and socializing, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bytes &amp; Bites @ Krog St Market</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>11:45 AM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Krog St Market, Georgia</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/313367802/?recId=07478199-cd17-44a9-b2f3-8b457041a5a2&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>The event has no mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its Georgia in-person location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Happy Birthday OWASP! 25 Year Anniversary Party</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/owasp-atlanta/events/315447074/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>The event is a birthday party celebration with no mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>🎬 404 Movie Not Found: Spider-Man (Matinee)</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/314126109/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is a movie screening event, which triggers the automatic 1 rating regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Introduction to Screenwriting</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/315319996/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Women who Woodwork (or want to!)</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/315325716/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>🎬☕ Write Once. Run Forever: The Java Story – AJUG Watch Party</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlantajug/events/315471818/?recId=6a09281b-d8ac-40bb-9558-113db160090b&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is about Java programming history, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Pitch, Please! Selling Service Design</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/service-design-network-atlanta/events/315575614/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Monitoring the Situation: Bitcoin News Night @ Manuel's Tavern</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, Georgia</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlantabitdevs/events/315045047/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation - it is a Bitcoin news discussion at a tavern, which triggers the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #1</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlantabitdevs/events/315045088/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ATL BitLab, Georgia</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlantabitdevs/events/315045016/?recId=f179649a-5cd3-46fc-9bfe-32fe8a4ba6e9&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a Bitcoin/cryptocurrency meetup, which triggers the automatic 1 rating regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #8</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlantabitdevs/events/315044809/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description (Bitcoin Builders is about cryptocurrency, not AI), which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Conyers WordPress Monthly Meetup</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Conyers, Georgia</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/conyers-wordpress-meetup/events/315537588/?recId=b02557e9-0af9-428c-8f8f-89e199ac5cfa&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering automatic score of 1 per criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/wordpress-gwinnett/events/315474486/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jewelry Makers Meetup</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/decatur-makers/events/315578008/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is a jewelry makers meetup with no AI content, which triggers an automatic 1 rating regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Arduino/Raspberry Pi User's Group</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/decatur-makers/events/315541561/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Inside SQLx: How Rust Checks SQL Before Your Application Runs</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/the-ubuntu-techhive-north-america/events/315365244/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation—it is about Rust and SQL compilation, which triggers the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Lunch @ Wire Park</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>11:45 AM</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Wire Park, Georgia</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/developers-of-athens/events/315233413/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>First Discussion at Cafe Intermezzo (Dunwoody): The Apple FBI iPhone case</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Cafe Intermezzo, Dunwoody, Georgia</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-white-hat-hacking-the-acropolis-guard-meetup/events/315468763/?recId=00a46071-9969-4bed-8713-44586ff0abd6&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, discussing instead a historical legal case between Apple and the FBI regarding iPhone security, which automatically qualifies it as a poor fit regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Tech / STEM - Bible Study</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/act-association-of-christian-technologists/events/315353931/?recId=261b62a2-b8c8-4719-93bf-7d39603f99e3&amp;recSource=ml-popular-events-nearby-online&amp;searchId=410f3c6b-af89-4207-97b9-a3ad4cf7c011&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation—it is a Bible study group for Christian technologists with no AI content specified, triggering the automatic 1 rating.</t>
         </is>
       </c>
     </row>
